--- a/research/traditional_assets/database/data/belgium/belgium_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_retail_grocery_and_food.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07357945677996255</v>
+        <v>0.07342925813801263</v>
       </c>
       <c r="C2">
-        <v>5408.429298280385</v>
+        <v>5376.183791020186</v>
       </c>
       <c r="D2">
-        <v>4621.329298280384</v>
+        <v>4646.451847034242</v>
       </c>
       <c r="E2">
-        <v>-1119.70560140569</v>
+        <v>-1062.337545391634</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>57.36805601405691</v>
       </c>
       <c r="G2">
         <v>787.1</v>
@@ -1451,28 +1451,28 @@
         <v>428.91</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.885613217507062</v>
       </c>
       <c r="N2">
-        <v>428.91</v>
+        <v>426.024386782493</v>
       </c>
       <c r="O2">
-        <v>107.2275</v>
+        <v>106.5060966956232</v>
       </c>
       <c r="P2">
-        <v>321.6825</v>
+        <v>319.5182900868697</v>
       </c>
       <c r="Q2">
-        <v>748.3824999999999</v>
+        <v>746.2182900868697</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07357945677996255</v>
+        <v>0.07378990721011378</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.5455753891120112</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>148.6373840394811</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07342925813801263</v>
+        <v>0.07327905949606274</v>
       </c>
       <c r="C3">
-        <v>5376.183791020186</v>
+        <v>5344.212919993849</v>
       </c>
       <c r="D3">
-        <v>4646.451847034242</v>
+        <v>4671.849032021963</v>
       </c>
       <c r="E3">
-        <v>-1062.337545391634</v>
+        <v>-1004.969489377577</v>
       </c>
       <c r="F3">
-        <v>57.36805601405691</v>
+        <v>114.7361120281138</v>
       </c>
       <c r="G3">
         <v>787.1</v>
@@ -1533,28 +1533,28 @@
         <v>428.91</v>
       </c>
       <c r="M3">
-        <v>2.885613217507062</v>
+        <v>5.771226435014125</v>
       </c>
       <c r="N3">
-        <v>426.024386782493</v>
+        <v>423.1387735649859</v>
       </c>
       <c r="O3">
-        <v>106.5060966956232</v>
+        <v>105.7846933912465</v>
       </c>
       <c r="P3">
-        <v>319.5182900868697</v>
+        <v>317.3540801737394</v>
       </c>
       <c r="Q3">
-        <v>746.2182900868697</v>
+        <v>744.0540801737394</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07378990721011378</v>
+        <v>0.07400465254700279</v>
       </c>
       <c r="T3">
-        <v>0.5455753891120112</v>
+        <v>0.5497611754332634</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>148.6373840394811</v>
+        <v>74.31869201974057</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07327905949606274</v>
+        <v>0.07312886085411283</v>
       </c>
       <c r="C4">
-        <v>5344.212919993849</v>
+        <v>5312.521213380177</v>
       </c>
       <c r="D4">
-        <v>4671.849032021963</v>
+        <v>4697.525381422347</v>
       </c>
       <c r="E4">
-        <v>-1004.969489377577</v>
+        <v>-947.6014333635197</v>
       </c>
       <c r="F4">
-        <v>114.7361120281138</v>
+        <v>172.1041680421707</v>
       </c>
       <c r="G4">
         <v>787.1</v>
@@ -1615,28 +1615,28 @@
         <v>428.91</v>
       </c>
       <c r="M4">
-        <v>5.771226435014125</v>
+        <v>8.656839652521187</v>
       </c>
       <c r="N4">
-        <v>423.1387735649859</v>
+        <v>420.2531603474789</v>
       </c>
       <c r="O4">
-        <v>105.7846933912465</v>
+        <v>105.0632900868697</v>
       </c>
       <c r="P4">
-        <v>317.3540801737394</v>
+        <v>315.1898702606092</v>
       </c>
       <c r="Q4">
-        <v>744.0540801737394</v>
+        <v>741.8898702606091</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07400465254700279</v>
+        <v>0.07422382562279672</v>
       </c>
       <c r="T4">
-        <v>0.5497611754332634</v>
+        <v>0.5540332666271187</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>74.31869201974057</v>
+        <v>49.54579467982705</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07312886085411283</v>
+        <v>0.07297866221216293</v>
       </c>
       <c r="C5">
-        <v>5312.521213380177</v>
+        <v>5281.113299455052</v>
       </c>
       <c r="D5">
-        <v>4697.525381422347</v>
+        <v>4723.485523511279</v>
       </c>
       <c r="E5">
-        <v>-947.6014333635197</v>
+        <v>-890.2333773494628</v>
       </c>
       <c r="F5">
-        <v>172.1041680421707</v>
+        <v>229.4722240562276</v>
       </c>
       <c r="G5">
         <v>787.1</v>
@@ -1697,28 +1697,28 @@
         <v>428.91</v>
       </c>
       <c r="M5">
-        <v>8.656839652521187</v>
+        <v>11.54245287002825</v>
       </c>
       <c r="N5">
-        <v>420.2531603474789</v>
+        <v>417.3675471299718</v>
       </c>
       <c r="O5">
-        <v>105.0632900868697</v>
+        <v>104.3418867824929</v>
       </c>
       <c r="P5">
-        <v>315.1898702606092</v>
+        <v>313.0256603474788</v>
       </c>
       <c r="Q5">
-        <v>741.8898702606091</v>
+        <v>739.7256603474789</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07422382562279672</v>
+        <v>0.07444756480433638</v>
       </c>
       <c r="T5">
-        <v>0.5540332666271187</v>
+        <v>0.5583943597208461</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.54579467982705</v>
+        <v>37.15934600987028</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07297866221216293</v>
+        <v>0.07282846357021301</v>
       </c>
       <c r="C6">
-        <v>5281.113299455052</v>
+        <v>5249.993909372689</v>
       </c>
       <c r="D6">
-        <v>4723.485523511279</v>
+        <v>4749.734189442973</v>
       </c>
       <c r="E6">
-        <v>-890.2333773494628</v>
+        <v>-832.865321335406</v>
       </c>
       <c r="F6">
-        <v>229.4722240562276</v>
+        <v>286.8402800702846</v>
       </c>
       <c r="G6">
         <v>787.1</v>
@@ -1779,28 +1779,28 @@
         <v>428.91</v>
       </c>
       <c r="M6">
-        <v>11.54245287002825</v>
+        <v>14.42806608753531</v>
       </c>
       <c r="N6">
-        <v>417.3675471299718</v>
+        <v>414.4819339124647</v>
       </c>
       <c r="O6">
-        <v>104.3418867824929</v>
+        <v>103.6204834781162</v>
       </c>
       <c r="P6">
-        <v>313.0256603474788</v>
+        <v>310.8614504343485</v>
       </c>
       <c r="Q6">
-        <v>739.7256603474789</v>
+        <v>737.5614504343484</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07444756480433638</v>
+        <v>0.07467601428443475</v>
       </c>
       <c r="T6">
-        <v>0.5583943597208461</v>
+        <v>0.5628472653007571</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.15934600987028</v>
+        <v>29.72747680789622</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07282846357021301</v>
+        <v>0.07267826492826311</v>
       </c>
       <c r="C7">
-        <v>5249.993909372689</v>
+        <v>5219.167880040092</v>
       </c>
       <c r="D7">
-        <v>4749.734189442973</v>
+        <v>4776.276216124434</v>
       </c>
       <c r="E7">
-        <v>-832.865321335406</v>
+        <v>-775.497265321349</v>
       </c>
       <c r="F7">
-        <v>286.8402800702846</v>
+        <v>344.2083360843415</v>
       </c>
       <c r="G7">
         <v>787.1</v>
@@ -1861,28 +1861,28 @@
         <v>428.91</v>
       </c>
       <c r="M7">
-        <v>14.42806608753531</v>
+        <v>17.31367930504238</v>
       </c>
       <c r="N7">
-        <v>414.4819339124647</v>
+        <v>411.5963206949576</v>
       </c>
       <c r="O7">
-        <v>103.6204834781162</v>
+        <v>102.8990801737394</v>
       </c>
       <c r="P7">
-        <v>310.8614504343485</v>
+        <v>308.6972405212182</v>
       </c>
       <c r="Q7">
-        <v>737.5614504343484</v>
+        <v>735.3972405212182</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07467601428443475</v>
+        <v>0.07490932439176927</v>
       </c>
       <c r="T7">
-        <v>0.5628472653007571</v>
+        <v>0.5673949135525812</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.72747680789622</v>
+        <v>24.77289733991352</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07267826492826311</v>
+        <v>0.07252806628631321</v>
       </c>
       <c r="C8">
-        <v>5219.167880040092</v>
+        <v>5188.640157088472</v>
       </c>
       <c r="D8">
-        <v>4776.276216124434</v>
+        <v>4803.11654918687</v>
       </c>
       <c r="E8">
-        <v>-775.497265321349</v>
+        <v>-718.1292093072921</v>
       </c>
       <c r="F8">
-        <v>344.2083360843415</v>
+        <v>401.5763920983983</v>
       </c>
       <c r="G8">
         <v>787.1</v>
@@ -1943,28 +1943,28 @@
         <v>428.91</v>
       </c>
       <c r="M8">
-        <v>17.31367930504237</v>
+        <v>20.19929252254943</v>
       </c>
       <c r="N8">
-        <v>411.5963206949576</v>
+        <v>408.7107074774506</v>
       </c>
       <c r="O8">
-        <v>102.8990801737394</v>
+        <v>102.1776768693626</v>
       </c>
       <c r="P8">
-        <v>308.6972405212182</v>
+        <v>306.5330306080879</v>
       </c>
       <c r="Q8">
-        <v>735.3972405212182</v>
+        <v>733.2330306080879</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07490932439176927</v>
+        <v>0.07514765192076689</v>
       </c>
       <c r="T8">
-        <v>0.5673949135525812</v>
+        <v>0.5720403606915412</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.77289733991352</v>
+        <v>21.23391200564016</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0725280662863132</v>
+        <v>0.0723778676443633</v>
       </c>
       <c r="C9">
-        <v>5188.640157088474</v>
+        <v>5158.415797945372</v>
       </c>
       <c r="D9">
-        <v>4803.116549186871</v>
+        <v>4830.260246057827</v>
       </c>
       <c r="E9">
-        <v>-718.1292093072921</v>
+        <v>-660.7611532932351</v>
       </c>
       <c r="F9">
-        <v>401.5763920983984</v>
+        <v>458.9444481124553</v>
       </c>
       <c r="G9">
         <v>787.1</v>
@@ -2025,28 +2025,28 @@
         <v>428.91</v>
       </c>
       <c r="M9">
-        <v>20.19929252254944</v>
+        <v>23.0849057400565</v>
       </c>
       <c r="N9">
-        <v>408.7107074774506</v>
+        <v>405.8250942599435</v>
       </c>
       <c r="O9">
-        <v>102.1776768693626</v>
+        <v>101.4562735649859</v>
       </c>
       <c r="P9">
-        <v>306.5330306080879</v>
+        <v>304.3688206949577</v>
       </c>
       <c r="Q9">
-        <v>733.2330306080879</v>
+        <v>731.0688206949576</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07514765192076689</v>
+        <v>0.07539116048300359</v>
       </c>
       <c r="T9">
-        <v>0.5720403606915412</v>
+        <v>0.576786795811783</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.23391200564016</v>
+        <v>18.57967300493514</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0723778676443633</v>
+        <v>0.0722276690024134</v>
       </c>
       <c r="C10">
-        <v>5158.415797945372</v>
+        <v>5128.499975011585</v>
       </c>
       <c r="D10">
-        <v>4830.260246057827</v>
+        <v>4857.712479138097</v>
       </c>
       <c r="E10">
-        <v>-660.7611532932351</v>
+        <v>-603.3930972791783</v>
       </c>
       <c r="F10">
-        <v>458.9444481124553</v>
+        <v>516.3125041265122</v>
       </c>
       <c r="G10">
         <v>787.1</v>
@@ -2107,28 +2107,28 @@
         <v>428.91</v>
       </c>
       <c r="M10">
-        <v>23.0849057400565</v>
+        <v>25.97051895756356</v>
       </c>
       <c r="N10">
-        <v>405.8250942599435</v>
+        <v>402.9394810424365</v>
       </c>
       <c r="O10">
-        <v>101.4562735649859</v>
+        <v>100.7348702606091</v>
       </c>
       <c r="P10">
-        <v>304.3688206949577</v>
+        <v>302.2046107818273</v>
       </c>
       <c r="Q10">
-        <v>731.0688206949576</v>
+        <v>728.9046107818274</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07539116048300359</v>
+        <v>0.07564002088177296</v>
       </c>
       <c r="T10">
-        <v>0.576786795811783</v>
+        <v>0.5816375481874148</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.57967300493514</v>
+        <v>16.51526489327568</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0722276690024134</v>
+        <v>0.07207747036046348</v>
       </c>
       <c r="C11">
-        <v>5128.499975011585</v>
+        <v>5098.897978947023</v>
       </c>
       <c r="D11">
-        <v>4857.712479138097</v>
+        <v>4885.478539087591</v>
       </c>
       <c r="E11">
-        <v>-603.3930972791783</v>
+        <v>-546.0250412651214</v>
       </c>
       <c r="F11">
-        <v>516.3125041265122</v>
+        <v>573.680560140569</v>
       </c>
       <c r="G11">
         <v>787.1</v>
@@ -2189,28 +2189,28 @@
         <v>428.91</v>
       </c>
       <c r="M11">
-        <v>25.97051895756356</v>
+        <v>28.85613217507062</v>
       </c>
       <c r="N11">
-        <v>402.9394810424365</v>
+        <v>400.0538678249294</v>
       </c>
       <c r="O11">
-        <v>100.7348702606091</v>
+        <v>100.0134669562323</v>
       </c>
       <c r="P11">
-        <v>302.2046107818273</v>
+        <v>300.040400868697</v>
       </c>
       <c r="Q11">
-        <v>728.9046107818274</v>
+        <v>726.740400868697</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07564002088177296</v>
+        <v>0.0758944115116261</v>
       </c>
       <c r="T11">
-        <v>0.5816375481874148</v>
+        <v>0.5865960950602827</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.51526489327568</v>
+        <v>14.86373840394812</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07207747036046348</v>
+        <v>0.07192727171851357</v>
       </c>
       <c r="C12">
-        <v>5098.897978947022</v>
+        <v>5069.6152220699</v>
       </c>
       <c r="D12">
-        <v>4885.478539087591</v>
+        <v>4913.563838224525</v>
       </c>
       <c r="E12">
-        <v>-546.0250412651213</v>
+        <v>-488.6569852510644</v>
       </c>
       <c r="F12">
-        <v>573.6805601405691</v>
+        <v>631.0486161546261</v>
       </c>
       <c r="G12">
         <v>787.1</v>
@@ -2271,28 +2271,28 @@
         <v>428.91</v>
       </c>
       <c r="M12">
-        <v>28.85613217507063</v>
+        <v>31.74174539257769</v>
       </c>
       <c r="N12">
-        <v>400.0538678249294</v>
+        <v>397.1682546074223</v>
       </c>
       <c r="O12">
-        <v>100.0134669562323</v>
+        <v>99.29206365185559</v>
       </c>
       <c r="P12">
-        <v>300.040400868697</v>
+        <v>297.8761909555668</v>
       </c>
       <c r="Q12">
-        <v>726.740400868697</v>
+        <v>724.5761909555667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0758944115116261</v>
+        <v>0.07615451878484672</v>
       </c>
       <c r="T12">
-        <v>0.5865960950602827</v>
+        <v>0.5916660699527657</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.86373840394811</v>
+        <v>13.51248945813465</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07192727171851357</v>
+        <v>0.07191207307656368</v>
       </c>
       <c r="C13">
-        <v>5069.6152220699</v>
+        <v>5015.107126552128</v>
       </c>
       <c r="D13">
-        <v>4913.563838224525</v>
+        <v>4916.423798720811</v>
       </c>
       <c r="E13">
-        <v>-488.6569852510644</v>
+        <v>-431.2889292370076</v>
       </c>
       <c r="F13">
-        <v>631.0486161546261</v>
+        <v>688.4166721686829</v>
       </c>
       <c r="G13">
         <v>787.1</v>
@@ -2353,45 +2353,45 @@
         <v>428.91</v>
       </c>
       <c r="M13">
-        <v>31.74174539257769</v>
+        <v>35.65998361833778</v>
       </c>
       <c r="N13">
-        <v>397.1682546074223</v>
+        <v>393.2500163816622</v>
       </c>
       <c r="O13">
-        <v>99.29206365185559</v>
+        <v>98.31250409541556</v>
       </c>
       <c r="P13">
-        <v>297.8761909555668</v>
+        <v>294.9375122862467</v>
       </c>
       <c r="Q13">
-        <v>724.5761909555667</v>
+        <v>721.6375122862466</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07615451878484672</v>
+        <v>0.07642053758700418</v>
       </c>
       <c r="T13">
-        <v>0.5916660699527657</v>
+        <v>0.5968512715473506</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.51248945813465</v>
+        <v>12.02776772391554</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07191207307656368</v>
+        <v>0.07177312443461376</v>
       </c>
       <c r="C14">
-        <v>5015.107126552128</v>
+        <v>4984.040504229743</v>
       </c>
       <c r="D14">
-        <v>4916.423798720811</v>
+        <v>4942.725232412483</v>
       </c>
       <c r="E14">
-        <v>-431.2889292370076</v>
+        <v>-373.9208732229506</v>
       </c>
       <c r="F14">
-        <v>688.4166721686829</v>
+        <v>745.7847281827399</v>
       </c>
       <c r="G14">
         <v>787.1</v>
@@ -2435,28 +2435,28 @@
         <v>428.91</v>
       </c>
       <c r="M14">
-        <v>35.65998361833778</v>
+        <v>38.63164891986592</v>
       </c>
       <c r="N14">
-        <v>393.2500163816622</v>
+        <v>390.2783510801341</v>
       </c>
       <c r="O14">
-        <v>98.31250409541556</v>
+        <v>97.56958777003352</v>
       </c>
       <c r="P14">
-        <v>294.9375122862467</v>
+        <v>292.7087633101006</v>
       </c>
       <c r="Q14">
-        <v>721.6375122862466</v>
+        <v>719.4087633101005</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07642053758700418</v>
+        <v>0.07669267176392386</v>
       </c>
       <c r="T14">
-        <v>0.5968512715473506</v>
+        <v>0.6021556731785925</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.02776772391554</v>
+        <v>11.10255482207588</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07177312443461376</v>
+        <v>0.07163417579266385</v>
       </c>
       <c r="C15">
-        <v>4984.040504229743</v>
+        <v>4953.256805467381</v>
       </c>
       <c r="D15">
-        <v>4942.725232412483</v>
+        <v>4969.309589664178</v>
       </c>
       <c r="E15">
-        <v>-373.9208732229506</v>
+        <v>-316.5528172088937</v>
       </c>
       <c r="F15">
-        <v>745.7847281827399</v>
+        <v>803.1527841967968</v>
       </c>
       <c r="G15">
         <v>787.1</v>
@@ -2517,28 +2517,28 @@
         <v>428.91</v>
       </c>
       <c r="M15">
-        <v>38.63164891986592</v>
+        <v>41.60331422139407</v>
       </c>
       <c r="N15">
-        <v>390.2783510801341</v>
+        <v>387.3066857786059</v>
       </c>
       <c r="O15">
-        <v>97.56958777003352</v>
+        <v>96.82667144465148</v>
       </c>
       <c r="P15">
-        <v>292.7087633101006</v>
+        <v>290.4800143339544</v>
       </c>
       <c r="Q15">
-        <v>719.4087633101005</v>
+        <v>717.1800143339544</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07669267176392386</v>
+        <v>0.07697113464263239</v>
       </c>
       <c r="T15">
-        <v>0.6021556731785925</v>
+        <v>0.6075834329873053</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.10255482207588</v>
+        <v>10.30951519192761</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07163417579266385</v>
+        <v>0.07168647715071395</v>
       </c>
       <c r="C16">
-        <v>4953.256805467381</v>
+        <v>4885.848695003363</v>
       </c>
       <c r="D16">
-        <v>4969.309589664178</v>
+        <v>4959.269535214216</v>
       </c>
       <c r="E16">
-        <v>-316.5528172088937</v>
+        <v>-259.1847611948367</v>
       </c>
       <c r="F16">
-        <v>803.1527841967968</v>
+        <v>860.5208402108537</v>
       </c>
       <c r="G16">
         <v>787.1</v>
@@ -2599,45 +2599,45 @@
         <v>428.91</v>
       </c>
       <c r="M16">
-        <v>41.60331422139407</v>
+        <v>46.03786495128067</v>
       </c>
       <c r="N16">
-        <v>387.3066857786059</v>
+        <v>382.8721350487194</v>
       </c>
       <c r="O16">
-        <v>96.82667144465148</v>
+        <v>95.71803376217984</v>
       </c>
       <c r="P16">
-        <v>290.4800143339544</v>
+        <v>287.1541012865395</v>
       </c>
       <c r="Q16">
-        <v>717.1800143339544</v>
+        <v>713.8541012865395</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07697113464263239</v>
+        <v>0.07725614958907524</v>
       </c>
       <c r="T16">
-        <v>0.6075834329873053</v>
+        <v>0.6131389047915172</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.30951519192761</v>
+        <v>9.31646157904785</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07168647715071395</v>
+        <v>0.07156027850876405</v>
       </c>
       <c r="C17">
-        <v>4885.848695003363</v>
+        <v>4852.775915152359</v>
       </c>
       <c r="D17">
-        <v>4959.269535214216</v>
+        <v>4983.564811377269</v>
       </c>
       <c r="E17">
-        <v>-259.1847611948368</v>
+        <v>-201.8167051807799</v>
       </c>
       <c r="F17">
-        <v>860.5208402108536</v>
+        <v>917.8888962249106</v>
       </c>
       <c r="G17">
         <v>787.1</v>
@@ -2681,28 +2681,28 @@
         <v>428.91</v>
       </c>
       <c r="M17">
-        <v>46.03786495128067</v>
+        <v>49.10705594803272</v>
       </c>
       <c r="N17">
-        <v>382.8721350487194</v>
+        <v>379.8029440519673</v>
       </c>
       <c r="O17">
-        <v>95.71803376217984</v>
+        <v>94.95073601299183</v>
       </c>
       <c r="P17">
-        <v>287.1541012865395</v>
+        <v>284.8522080389755</v>
       </c>
       <c r="Q17">
-        <v>713.8541012865395</v>
+        <v>711.5522080389756</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07725614958907524</v>
+        <v>0.07754795060567149</v>
       </c>
       <c r="T17">
-        <v>0.6131389047915172</v>
+        <v>0.6188266497339246</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.316461579047852</v>
+        <v>8.734182730357361</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07156027850876405</v>
+        <v>0.07143407986681415</v>
       </c>
       <c r="C18">
-        <v>4852.775915152359</v>
+        <v>4819.942350508101</v>
       </c>
       <c r="D18">
-        <v>4983.564811377269</v>
+        <v>5008.099302747069</v>
       </c>
       <c r="E18">
-        <v>-201.8167051807799</v>
+        <v>-144.4486491667229</v>
       </c>
       <c r="F18">
-        <v>917.8888962249106</v>
+        <v>975.2569522389675</v>
       </c>
       <c r="G18">
         <v>787.1</v>
@@ -2763,28 +2763,28 @@
         <v>428.91</v>
       </c>
       <c r="M18">
-        <v>49.10705594803272</v>
+        <v>52.17624694478476</v>
       </c>
       <c r="N18">
-        <v>379.8029440519673</v>
+        <v>376.7337530552153</v>
       </c>
       <c r="O18">
-        <v>94.95073601299183</v>
+        <v>94.18343826380382</v>
       </c>
       <c r="P18">
-        <v>284.8522080389755</v>
+        <v>282.5503147914114</v>
       </c>
       <c r="Q18">
-        <v>711.5522080389756</v>
+        <v>709.2503147914115</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07754795060567149</v>
+        <v>0.07784678297206524</v>
       </c>
       <c r="T18">
-        <v>0.6188266497339246</v>
+        <v>0.6246514487713298</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.734182730357361</v>
+        <v>8.220407275630457</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07143407986681415</v>
+        <v>0.07130788122486423</v>
       </c>
       <c r="C19">
-        <v>4819.942350508101</v>
+        <v>4787.351551577278</v>
       </c>
       <c r="D19">
-        <v>5008.099302747069</v>
+        <v>5032.876559830302</v>
       </c>
       <c r="E19">
-        <v>-144.4486491667229</v>
+        <v>-87.08059315266587</v>
       </c>
       <c r="F19">
-        <v>975.2569522389675</v>
+        <v>1032.625008253025</v>
       </c>
       <c r="G19">
         <v>787.1</v>
@@ -2845,28 +2845,28 @@
         <v>428.91</v>
       </c>
       <c r="M19">
-        <v>52.17624694478476</v>
+        <v>55.24543794153681</v>
       </c>
       <c r="N19">
-        <v>376.7337530552153</v>
+        <v>373.6645620584632</v>
       </c>
       <c r="O19">
-        <v>94.18343826380382</v>
+        <v>93.4161405146158</v>
       </c>
       <c r="P19">
-        <v>282.5503147914114</v>
+        <v>280.2484215438474</v>
       </c>
       <c r="Q19">
-        <v>709.2503147914115</v>
+        <v>706.9484215438474</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07784678297206524</v>
+        <v>0.07815290393276125</v>
       </c>
       <c r="T19">
-        <v>0.6246514487713298</v>
+        <v>0.6306183160779399</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.220407275630457</v>
+        <v>7.763717982539875</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07130788122486423</v>
+        <v>0.07129568258291434</v>
       </c>
       <c r="C20">
-        <v>4787.351551577278</v>
+        <v>4732.391521272345</v>
       </c>
       <c r="D20">
-        <v>5032.876559830302</v>
+        <v>5035.284585539426</v>
       </c>
       <c r="E20">
-        <v>-87.0805931526661</v>
+        <v>-29.71253713860915</v>
       </c>
       <c r="F20">
-        <v>1032.625008253024</v>
+        <v>1089.993064267081</v>
       </c>
       <c r="G20">
         <v>787.1</v>
@@ -2927,45 +2927,45 @@
         <v>428.91</v>
       </c>
       <c r="M20">
-        <v>55.2454379415368</v>
+        <v>59.18662338970252</v>
       </c>
       <c r="N20">
-        <v>373.6645620584632</v>
+        <v>369.7233766102975</v>
       </c>
       <c r="O20">
-        <v>93.4161405146158</v>
+        <v>92.43084415257438</v>
       </c>
       <c r="P20">
-        <v>280.2484215438474</v>
+        <v>277.2925324577232</v>
       </c>
       <c r="Q20">
-        <v>706.9484215438474</v>
+        <v>703.9925324577232</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07815290393276125</v>
+        <v>0.07846658343569671</v>
       </c>
       <c r="T20">
-        <v>0.6306183160779399</v>
+        <v>0.6367325134415035</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.763717982539876</v>
+        <v>7.246738797311137</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07129568258291434</v>
+        <v>0.07117548394096443</v>
       </c>
       <c r="C21">
-        <v>4732.391521272345</v>
+        <v>4698.874611128895</v>
       </c>
       <c r="D21">
-        <v>5035.284585539426</v>
+        <v>5059.135731410032</v>
       </c>
       <c r="E21">
-        <v>-29.71253713860915</v>
+        <v>27.6555188754478</v>
       </c>
       <c r="F21">
-        <v>1089.993064267081</v>
+        <v>1147.361120281138</v>
       </c>
       <c r="G21">
         <v>787.1</v>
@@ -3009,28 +3009,28 @@
         <v>428.91</v>
       </c>
       <c r="M21">
-        <v>59.18662338970252</v>
+        <v>62.30170883126581</v>
       </c>
       <c r="N21">
-        <v>369.7233766102975</v>
+        <v>366.6082911687342</v>
       </c>
       <c r="O21">
-        <v>92.43084415257438</v>
+        <v>91.65207279218356</v>
       </c>
       <c r="P21">
-        <v>277.2925324577232</v>
+        <v>274.9562183765507</v>
       </c>
       <c r="Q21">
-        <v>703.9925324577232</v>
+        <v>701.6562183765507</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07846658343569671</v>
+        <v>0.07878810492620553</v>
       </c>
       <c r="T21">
-        <v>0.6367325134415035</v>
+        <v>0.6429995657391561</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.246738797311137</v>
+        <v>6.884401857445581</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07117548394096443</v>
+        <v>0.0710552852990145</v>
       </c>
       <c r="C22">
-        <v>4698.874611128895</v>
+        <v>4665.584732698504</v>
       </c>
       <c r="D22">
-        <v>5059.135731410032</v>
+        <v>5083.213908993699</v>
       </c>
       <c r="E22">
-        <v>27.6555188754478</v>
+        <v>85.02357488950474</v>
       </c>
       <c r="F22">
-        <v>1147.361120281138</v>
+        <v>1204.729176295195</v>
       </c>
       <c r="G22">
         <v>787.1</v>
@@ -3091,28 +3091,28 @@
         <v>428.91</v>
       </c>
       <c r="M22">
-        <v>62.30170883126581</v>
+        <v>65.41679427282909</v>
       </c>
       <c r="N22">
-        <v>366.6082911687342</v>
+        <v>363.4932057271709</v>
       </c>
       <c r="O22">
-        <v>91.65207279218356</v>
+        <v>90.87330143179273</v>
       </c>
       <c r="P22">
-        <v>274.9562183765507</v>
+        <v>272.6199042953782</v>
       </c>
       <c r="Q22">
-        <v>701.6562183765507</v>
+        <v>699.3199042953781</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07878810492620553</v>
+        <v>0.07911776620128419</v>
       </c>
       <c r="T22">
-        <v>0.6429995657391561</v>
+        <v>0.649425277588648</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.884401857445581</v>
+        <v>6.556573197567219</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0710552852990145</v>
+        <v>0.07093508665706462</v>
       </c>
       <c r="C23">
-        <v>4665.584732698504</v>
+        <v>4632.525143050132</v>
       </c>
       <c r="D23">
-        <v>5083.213908993699</v>
+        <v>5107.522375359384</v>
       </c>
       <c r="E23">
-        <v>85.02357488950452</v>
+        <v>142.3916309035617</v>
       </c>
       <c r="F23">
-        <v>1204.729176295195</v>
+        <v>1262.097232309252</v>
       </c>
       <c r="G23">
         <v>787.1</v>
@@ -3173,28 +3173,28 @@
         <v>428.91</v>
       </c>
       <c r="M23">
-        <v>65.41679427282909</v>
+        <v>68.53187971439239</v>
       </c>
       <c r="N23">
-        <v>363.4932057271709</v>
+        <v>360.3781202856076</v>
       </c>
       <c r="O23">
-        <v>90.87330143179273</v>
+        <v>90.09453007140191</v>
       </c>
       <c r="P23">
-        <v>272.6199042953782</v>
+        <v>270.2835902142057</v>
       </c>
       <c r="Q23">
-        <v>699.3199042953781</v>
+        <v>696.9835902142057</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07911776620128419</v>
+        <v>0.07945588032957002</v>
       </c>
       <c r="T23">
-        <v>0.649425277588648</v>
+        <v>0.6560157512804344</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.556573197567219</v>
+        <v>6.258547143132345</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07093508665706462</v>
+        <v>0.0709873880151147</v>
       </c>
       <c r="C24">
-        <v>4632.525143050132</v>
+        <v>4564.551368160334</v>
       </c>
       <c r="D24">
-        <v>5107.522375359384</v>
+        <v>5096.916656483643</v>
       </c>
       <c r="E24">
-        <v>142.3916309035617</v>
+        <v>199.7596869176186</v>
       </c>
       <c r="F24">
-        <v>1262.097232309252</v>
+        <v>1319.465288323309</v>
       </c>
       <c r="G24">
         <v>787.1</v>
@@ -3255,45 +3255,45 @@
         <v>428.91</v>
       </c>
       <c r="M24">
-        <v>68.53187971439239</v>
+        <v>72.966430444279</v>
       </c>
       <c r="N24">
-        <v>360.3781202856076</v>
+        <v>355.943569555721</v>
       </c>
       <c r="O24">
-        <v>90.09453007140191</v>
+        <v>88.98589238893025</v>
       </c>
       <c r="P24">
-        <v>270.2835902142057</v>
+        <v>266.9576771667907</v>
       </c>
       <c r="Q24">
-        <v>696.9835902142057</v>
+        <v>693.6576771667908</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07945588032957002</v>
+        <v>0.07980277664300611</v>
       </c>
       <c r="T24">
-        <v>0.6560157512804344</v>
+        <v>0.6627774061070727</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.258547143132345</v>
+        <v>5.878182575034121</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0709873880151147</v>
+        <v>0.0708746893731648</v>
       </c>
       <c r="C25">
-        <v>4564.551368160334</v>
+        <v>4530.091495644348</v>
       </c>
       <c r="D25">
-        <v>5096.916656483643</v>
+        <v>5119.824839981713</v>
       </c>
       <c r="E25">
-        <v>199.7596869176186</v>
+        <v>257.1277429316756</v>
       </c>
       <c r="F25">
-        <v>1319.465288323309</v>
+        <v>1376.833344337366</v>
       </c>
       <c r="G25">
         <v>787.1</v>
@@ -3337,28 +3337,28 @@
         <v>428.91</v>
       </c>
       <c r="M25">
-        <v>72.966430444279</v>
+        <v>76.13888394185635</v>
       </c>
       <c r="N25">
-        <v>355.943569555721</v>
+        <v>352.7711160581437</v>
       </c>
       <c r="O25">
-        <v>88.98589238893025</v>
+        <v>88.19277901453592</v>
       </c>
       <c r="P25">
-        <v>266.9576771667907</v>
+        <v>264.5783370436077</v>
       </c>
       <c r="Q25">
-        <v>693.6576771667908</v>
+        <v>691.2783370436077</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07980277664300611</v>
+        <v>0.08015880180679578</v>
       </c>
       <c r="T25">
-        <v>0.6627774061070727</v>
+        <v>0.6697169992186224</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.878182575034121</v>
+        <v>5.633258301074366</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0708746893731648</v>
+        <v>0.07076199073121489</v>
       </c>
       <c r="C26">
-        <v>4530.091495644348</v>
+        <v>4495.838475313954</v>
       </c>
       <c r="D26">
-        <v>5119.824839981713</v>
+        <v>5142.939875665377</v>
       </c>
       <c r="E26">
-        <v>257.1277429316754</v>
+        <v>314.4957989457323</v>
       </c>
       <c r="F26">
-        <v>1376.833344337366</v>
+        <v>1434.201400351423</v>
       </c>
       <c r="G26">
         <v>787.1</v>
@@ -3419,28 +3419,28 @@
         <v>428.91</v>
       </c>
       <c r="M26">
-        <v>76.13888394185634</v>
+        <v>79.31133743943369</v>
       </c>
       <c r="N26">
-        <v>352.7711160581437</v>
+        <v>349.5986625605664</v>
       </c>
       <c r="O26">
-        <v>88.19277901453592</v>
+        <v>87.39966564014159</v>
       </c>
       <c r="P26">
-        <v>264.5783370436077</v>
+        <v>262.1989969204247</v>
       </c>
       <c r="Q26">
-        <v>691.2783370436077</v>
+        <v>688.8989969204247</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08015880180679578</v>
+        <v>0.08052432097495318</v>
       </c>
       <c r="T26">
-        <v>0.6697169992186224</v>
+        <v>0.6768416481464801</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.633258301074367</v>
+        <v>5.407927969031393</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07076199073121489</v>
+        <v>0.07064929208926499</v>
       </c>
       <c r="C27">
-        <v>4495.838475313954</v>
+        <v>4461.795121570507</v>
       </c>
       <c r="D27">
-        <v>5142.939875665377</v>
+        <v>5166.264577935986</v>
       </c>
       <c r="E27">
-        <v>314.4957989457323</v>
+        <v>371.8638549597893</v>
       </c>
       <c r="F27">
-        <v>1434.201400351423</v>
+        <v>1491.56945636548</v>
       </c>
       <c r="G27">
         <v>787.1</v>
@@ -3501,28 +3501,28 @@
         <v>428.91</v>
       </c>
       <c r="M27">
-        <v>79.31133743943369</v>
+        <v>82.48379093701104</v>
       </c>
       <c r="N27">
-        <v>349.5986625605664</v>
+        <v>346.426209062989</v>
       </c>
       <c r="O27">
-        <v>87.39966564014159</v>
+        <v>86.60655226574724</v>
       </c>
       <c r="P27">
-        <v>262.1989969204247</v>
+        <v>259.8196567972417</v>
       </c>
       <c r="Q27">
-        <v>688.8989969204247</v>
+        <v>686.5196567972416</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08052432097495318</v>
+        <v>0.08089971903954728</v>
       </c>
       <c r="T27">
-        <v>0.6768416481464801</v>
+        <v>0.6841588551534691</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.407927969031393</v>
+        <v>5.199930739453261</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07064929208926499</v>
+        <v>0.07053659344731508</v>
       </c>
       <c r="C28">
-        <v>4461.795121570507</v>
+        <v>4427.964300104421</v>
       </c>
       <c r="D28">
-        <v>5166.264577935986</v>
+        <v>5189.801812483957</v>
       </c>
       <c r="E28">
-        <v>371.8638549597893</v>
+        <v>429.2319109738462</v>
       </c>
       <c r="F28">
-        <v>1491.56945636548</v>
+        <v>1548.937512379537</v>
       </c>
       <c r="G28">
         <v>787.1</v>
@@ -3583,28 +3583,28 @@
         <v>428.91</v>
       </c>
       <c r="M28">
-        <v>82.48379093701104</v>
+        <v>85.65624443458837</v>
       </c>
       <c r="N28">
-        <v>346.426209062989</v>
+        <v>343.2537555654117</v>
       </c>
       <c r="O28">
-        <v>86.60655226574724</v>
+        <v>85.81343889135292</v>
       </c>
       <c r="P28">
-        <v>259.8196567972417</v>
+        <v>257.4403166740587</v>
       </c>
       <c r="Q28">
-        <v>686.5196567972416</v>
+        <v>684.1403166740588</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08089971903954728</v>
+        <v>0.08128540198262341</v>
       </c>
       <c r="T28">
-        <v>0.6841588551534691</v>
+        <v>0.6916765335853071</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.199930739453261</v>
+        <v>5.007340712066104</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07053659344731508</v>
+        <v>0.07042389480536516</v>
       </c>
       <c r="C29">
-        <v>4427.964300104421</v>
+        <v>4394.348929068889</v>
       </c>
       <c r="D29">
-        <v>5189.801812483957</v>
+        <v>5213.554497462483</v>
       </c>
       <c r="E29">
-        <v>429.2319109738462</v>
+        <v>486.5999669879031</v>
       </c>
       <c r="F29">
-        <v>1548.937512379537</v>
+        <v>1606.305568393594</v>
       </c>
       <c r="G29">
         <v>787.1</v>
@@ -3665,28 +3665,28 @@
         <v>428.91</v>
       </c>
       <c r="M29">
-        <v>85.65624443458837</v>
+        <v>88.82869793216572</v>
       </c>
       <c r="N29">
-        <v>343.2537555654117</v>
+        <v>340.0813020678343</v>
       </c>
       <c r="O29">
-        <v>85.81343889135292</v>
+        <v>85.02032551695858</v>
       </c>
       <c r="P29">
-        <v>257.4403166740587</v>
+        <v>255.0609765508758</v>
       </c>
       <c r="Q29">
-        <v>684.1403166740588</v>
+        <v>681.7609765508757</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08128540198262341</v>
+        <v>0.08168179834078496</v>
       </c>
       <c r="T29">
-        <v>0.6916765335853071</v>
+        <v>0.6994030364180295</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.007340712066104</v>
+        <v>4.8285071152066</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07042389480536516</v>
+        <v>0.07031119616341526</v>
       </c>
       <c r="C30">
-        <v>4394.348929068889</v>
+        <v>4360.951980285936</v>
       </c>
       <c r="D30">
-        <v>5213.554497462483</v>
+        <v>5237.525604693587</v>
       </c>
       <c r="E30">
-        <v>486.5999669879031</v>
+        <v>543.9680230019601</v>
       </c>
       <c r="F30">
-        <v>1606.305568393594</v>
+        <v>1663.673624407651</v>
       </c>
       <c r="G30">
         <v>787.1</v>
@@ -3747,28 +3747,28 @@
         <v>428.91</v>
       </c>
       <c r="M30">
-        <v>88.82869793216572</v>
+        <v>92.00115142974308</v>
       </c>
       <c r="N30">
-        <v>340.0813020678343</v>
+        <v>336.908848570257</v>
       </c>
       <c r="O30">
-        <v>85.02032551695858</v>
+        <v>84.22721214256424</v>
       </c>
       <c r="P30">
-        <v>255.0609765508758</v>
+        <v>252.6816364276927</v>
       </c>
       <c r="Q30">
-        <v>681.7609765508757</v>
+        <v>679.3816364276927</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08168179834078496</v>
+        <v>0.08208936079354262</v>
       </c>
       <c r="T30">
-        <v>0.6994030364180295</v>
+        <v>0.7073471872178707</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.8285071152066</v>
+        <v>4.662006869854649</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07031119616341526</v>
+        <v>0.07019849752146536</v>
       </c>
       <c r="C31">
-        <v>4360.951980285937</v>
+        <v>4327.776480485945</v>
       </c>
       <c r="D31">
-        <v>5237.525604693587</v>
+        <v>5261.718160907652</v>
       </c>
       <c r="E31">
-        <v>543.9680230019599</v>
+        <v>601.3360790160168</v>
       </c>
       <c r="F31">
-        <v>1663.67362440765</v>
+        <v>1721.041680421707</v>
       </c>
       <c r="G31">
         <v>787.1</v>
@@ -3829,28 +3829,28 @@
         <v>428.91</v>
       </c>
       <c r="M31">
-        <v>92.00115142974306</v>
+        <v>95.17360492732041</v>
       </c>
       <c r="N31">
-        <v>336.908848570257</v>
+        <v>333.7363950726796</v>
       </c>
       <c r="O31">
-        <v>84.22721214256424</v>
+        <v>83.4340987681699</v>
       </c>
       <c r="P31">
-        <v>252.6816364276927</v>
+        <v>250.3022963045097</v>
       </c>
       <c r="Q31">
-        <v>679.3816364276927</v>
+        <v>677.0022963045096</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08208936079354262</v>
+        <v>0.08250856788780765</v>
       </c>
       <c r="T31">
-        <v>0.7073471872178707</v>
+        <v>0.7155183137548503</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.662006869854649</v>
+        <v>4.506606640859494</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07019849752146536</v>
+        <v>0.07066704887951544</v>
       </c>
       <c r="C32">
-        <v>4327.776480485945</v>
+        <v>4171.265771802679</v>
       </c>
       <c r="D32">
-        <v>5261.718160907652</v>
+        <v>5162.575508238442</v>
       </c>
       <c r="E32">
-        <v>601.3360790160168</v>
+        <v>658.7041350300738</v>
       </c>
       <c r="F32">
-        <v>1721.041680421707</v>
+        <v>1778.409736435764</v>
       </c>
       <c r="G32">
         <v>787.1</v>
@@ -3911,45 +3911,45 @@
         <v>428.91</v>
       </c>
       <c r="M32">
-        <v>95.17360492732041</v>
+        <v>102.7920827659872</v>
       </c>
       <c r="N32">
-        <v>333.7363950726796</v>
+        <v>326.1179172340129</v>
       </c>
       <c r="O32">
-        <v>83.4340987681699</v>
+        <v>81.52947930850321</v>
       </c>
       <c r="P32">
-        <v>250.3022963045097</v>
+        <v>244.5884379255097</v>
       </c>
       <c r="Q32">
-        <v>677.0022963045096</v>
+        <v>671.2884379255097</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08250856788780765</v>
+        <v>0.08293992591234123</v>
       </c>
       <c r="T32">
-        <v>0.7155183137548503</v>
+        <v>0.7239262845392787</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.506606640859494</v>
+        <v>4.172597620931968</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07066704887951544</v>
+        <v>0.07057310023756554</v>
       </c>
       <c r="C33">
-        <v>4171.265771802679</v>
+        <v>4133.476087220202</v>
       </c>
       <c r="D33">
-        <v>5162.575508238442</v>
+        <v>5182.153879670023</v>
       </c>
       <c r="E33">
-        <v>658.7041350300738</v>
+        <v>716.0721910441307</v>
       </c>
       <c r="F33">
-        <v>1778.409736435764</v>
+        <v>1835.777792449821</v>
       </c>
       <c r="G33">
         <v>787.1</v>
@@ -3993,28 +3993,28 @@
         <v>428.91</v>
       </c>
       <c r="M33">
-        <v>102.7920827659872</v>
+        <v>106.1079564035997</v>
       </c>
       <c r="N33">
-        <v>326.1179172340129</v>
+        <v>322.8020435964004</v>
       </c>
       <c r="O33">
-        <v>81.52947930850321</v>
+        <v>80.7005108991001</v>
       </c>
       <c r="P33">
-        <v>244.5884379255097</v>
+        <v>242.1015326973003</v>
       </c>
       <c r="Q33">
-        <v>671.2884379255097</v>
+        <v>668.8015326973002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08293992591234123</v>
+        <v>0.08338397093759639</v>
       </c>
       <c r="T33">
-        <v>0.7239262845392787</v>
+        <v>0.7325815485820726</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.172597620931968</v>
+        <v>4.042203945277844</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07057310023756554</v>
+        <v>0.07134540159561564</v>
       </c>
       <c r="C34">
-        <v>4133.476087220202</v>
+        <v>3919.43856316456</v>
       </c>
       <c r="D34">
-        <v>5182.153879670023</v>
+        <v>5025.484411628438</v>
       </c>
       <c r="E34">
-        <v>716.0721910441307</v>
+        <v>773.4402470581877</v>
       </c>
       <c r="F34">
-        <v>1835.777792449821</v>
+        <v>1893.145848463878</v>
       </c>
       <c r="G34">
         <v>787.1</v>
@@ -4075,45 +4075,45 @@
         <v>428.91</v>
       </c>
       <c r="M34">
-        <v>106.1079564035997</v>
+        <v>116.0498405108357</v>
       </c>
       <c r="N34">
-        <v>322.8020435964004</v>
+        <v>312.8601594891643</v>
       </c>
       <c r="O34">
-        <v>80.7005108991001</v>
+        <v>78.21503987229107</v>
       </c>
       <c r="P34">
-        <v>242.1015326973003</v>
+        <v>234.6451196168732</v>
       </c>
       <c r="Q34">
-        <v>668.8015326973002</v>
+        <v>661.3451196168733</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08338397093759639</v>
+        <v>0.0838412710382323</v>
       </c>
       <c r="T34">
-        <v>0.7325815485820726</v>
+        <v>0.7414951787156961</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.042203945277844</v>
+        <v>3.69591201600964</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07134540159561564</v>
+        <v>0.07127770295366573</v>
       </c>
       <c r="C35">
-        <v>3919.43856316456</v>
+        <v>3875.42408421459</v>
       </c>
       <c r="D35">
-        <v>5025.484411628438</v>
+        <v>5038.837988692525</v>
       </c>
       <c r="E35">
-        <v>773.4402470581877</v>
+        <v>830.8083030722446</v>
       </c>
       <c r="F35">
-        <v>1893.145848463878</v>
+        <v>1950.513904477935</v>
       </c>
       <c r="G35">
         <v>787.1</v>
@@ -4157,28 +4157,28 @@
         <v>428.91</v>
       </c>
       <c r="M35">
-        <v>116.0498405108357</v>
+        <v>119.5665023444974</v>
       </c>
       <c r="N35">
-        <v>312.8601594891643</v>
+        <v>309.3434976555026</v>
       </c>
       <c r="O35">
-        <v>78.21503987229107</v>
+        <v>77.33587441387564</v>
       </c>
       <c r="P35">
-        <v>234.6451196168732</v>
+        <v>232.0076232416269</v>
       </c>
       <c r="Q35">
-        <v>661.3451196168733</v>
+        <v>658.7076232416269</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0838412710382323</v>
+        <v>0.08431242871767536</v>
       </c>
       <c r="T35">
-        <v>0.7414951787156961</v>
+        <v>0.7506789188533689</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.69591201600964</v>
+        <v>3.587208721421121</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07127770295366573</v>
+        <v>0.07194500431171583</v>
       </c>
       <c r="C36">
-        <v>3875.42408421459</v>
+        <v>3689.44930116541</v>
       </c>
       <c r="D36">
-        <v>5038.837988692525</v>
+        <v>4910.231261657402</v>
       </c>
       <c r="E36">
-        <v>830.8083030722446</v>
+        <v>888.1763590863015</v>
       </c>
       <c r="F36">
-        <v>1950.513904477935</v>
+        <v>2007.881960491992</v>
       </c>
       <c r="G36">
         <v>787.1</v>
@@ -4239,45 +4239,45 @@
         <v>428.91</v>
       </c>
       <c r="M36">
-        <v>119.5665023444974</v>
+        <v>128.7052336675367</v>
       </c>
       <c r="N36">
-        <v>309.3434976555026</v>
+        <v>300.2047663324634</v>
       </c>
       <c r="O36">
-        <v>77.33587441387564</v>
+        <v>75.05119158311584</v>
       </c>
       <c r="P36">
-        <v>232.0076232416269</v>
+        <v>225.1535747493475</v>
       </c>
       <c r="Q36">
-        <v>658.7076232416269</v>
+        <v>651.8535747493474</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08431242871767536</v>
+        <v>0.08479808355648588</v>
       </c>
       <c r="T36">
-        <v>0.7506789188533689</v>
+        <v>0.7601452356106623</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.587208721421121</v>
+        <v>3.332498514457722</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07194500431171583</v>
+        <v>0.07189830566976591</v>
       </c>
       <c r="C37">
-        <v>3689.44930116541</v>
+        <v>3640.867299483037</v>
       </c>
       <c r="D37">
-        <v>4910.231261657402</v>
+        <v>4919.017315989086</v>
       </c>
       <c r="E37">
-        <v>888.1763590863015</v>
+        <v>945.5444151003587</v>
       </c>
       <c r="F37">
-        <v>2007.881960491992</v>
+        <v>2065.250016506049</v>
       </c>
       <c r="G37">
         <v>787.1</v>
@@ -4321,28 +4321,28 @@
         <v>428.91</v>
       </c>
       <c r="M37">
-        <v>128.7052336675367</v>
+        <v>132.3825260580378</v>
       </c>
       <c r="N37">
-        <v>300.2047663324634</v>
+        <v>296.5274739419623</v>
       </c>
       <c r="O37">
-        <v>75.05119158311584</v>
+        <v>74.13186848549057</v>
       </c>
       <c r="P37">
-        <v>225.1535747493475</v>
+        <v>222.3956054564717</v>
       </c>
       <c r="Q37">
-        <v>651.8535747493474</v>
+        <v>649.0956054564717</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08479808355648588</v>
+        <v>0.08529891510900925</v>
       </c>
       <c r="T37">
-        <v>0.7601452356106623</v>
+        <v>0.7699073747666211</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.332498514457722</v>
+        <v>3.23992911127834</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07189830566976593</v>
+        <v>0.07185160702781601</v>
       </c>
       <c r="C38">
-        <v>3640.867299483032</v>
+        <v>3592.31679657192</v>
       </c>
       <c r="D38">
-        <v>4919.01731598908</v>
+        <v>4927.834869092026</v>
       </c>
       <c r="E38">
-        <v>945.5444151003583</v>
+        <v>1002.912471114415</v>
       </c>
       <c r="F38">
-        <v>2065.250016506049</v>
+        <v>2122.618072520106</v>
       </c>
       <c r="G38">
         <v>787.1</v>
@@ -4403,28 +4403,28 @@
         <v>428.91</v>
       </c>
       <c r="M38">
-        <v>132.3825260580377</v>
+        <v>136.0598184485388</v>
       </c>
       <c r="N38">
-        <v>296.5274739419623</v>
+        <v>292.8501815514612</v>
       </c>
       <c r="O38">
-        <v>74.13186848549057</v>
+        <v>73.2125453878653</v>
       </c>
       <c r="P38">
-        <v>222.3956054564717</v>
+        <v>219.6376361635959</v>
       </c>
       <c r="Q38">
-        <v>649.0956054564717</v>
+        <v>646.3376361635959</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08529891510900925</v>
+        <v>0.08581564607589844</v>
       </c>
       <c r="T38">
-        <v>0.7699073747666211</v>
+        <v>0.7799794231021342</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.239929111278341</v>
+        <v>3.152363459622169</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07185160702781601</v>
+        <v>0.07180490838586612</v>
       </c>
       <c r="C39">
-        <v>3592.31679657192</v>
+        <v>3543.797962125012</v>
       </c>
       <c r="D39">
-        <v>4927.834869092026</v>
+        <v>4936.684090659174</v>
       </c>
       <c r="E39">
-        <v>1002.912471114415</v>
+        <v>1060.280527128472</v>
       </c>
       <c r="F39">
-        <v>2122.618072520106</v>
+        <v>2179.986128534163</v>
       </c>
       <c r="G39">
         <v>787.1</v>
@@ -4485,28 +4485,28 @@
         <v>428.91</v>
       </c>
       <c r="M39">
-        <v>136.0598184485388</v>
+        <v>139.7371108390398</v>
       </c>
       <c r="N39">
-        <v>292.8501815514612</v>
+        <v>289.1728891609602</v>
       </c>
       <c r="O39">
-        <v>73.2125453878653</v>
+        <v>72.29322229024004</v>
       </c>
       <c r="P39">
-        <v>219.6376361635959</v>
+        <v>216.8796668707201</v>
       </c>
       <c r="Q39">
-        <v>646.3376361635959</v>
+        <v>643.5796668707201</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08581564607589844</v>
+        <v>0.08634904578365502</v>
       </c>
       <c r="T39">
-        <v>0.7799794231021342</v>
+        <v>0.7903763762226639</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.152363459622169</v>
+        <v>3.069406526474217</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07180490838586612</v>
+        <v>0.0740397097439162</v>
       </c>
       <c r="C40">
-        <v>3543.797962125012</v>
+        <v>3095.756332971764</v>
       </c>
       <c r="D40">
-        <v>4936.684090659174</v>
+        <v>4546.010517519983</v>
       </c>
       <c r="E40">
-        <v>1060.280527128472</v>
+        <v>1117.648583142529</v>
       </c>
       <c r="F40">
-        <v>2179.986128534163</v>
+        <v>2237.35418454822</v>
       </c>
       <c r="G40">
         <v>787.1</v>
@@ -4567,45 +4567,45 @@
         <v>428.91</v>
       </c>
       <c r="M40">
-        <v>139.7371108390398</v>
+        <v>160.865765869017</v>
       </c>
       <c r="N40">
-        <v>289.1728891609602</v>
+        <v>268.044234130983</v>
       </c>
       <c r="O40">
-        <v>72.29322229024004</v>
+        <v>67.01105853274575</v>
       </c>
       <c r="P40">
-        <v>216.8796668707201</v>
+        <v>201.0331755982372</v>
       </c>
       <c r="Q40">
-        <v>643.5796668707201</v>
+        <v>627.7331755982373</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08634904578365502</v>
+        <v>0.08689993400642</v>
       </c>
       <c r="T40">
-        <v>0.7903763762226639</v>
+        <v>0.8011142130520633</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.069406526474217</v>
+        <v>2.666260267888413</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0740397097439162</v>
+        <v>0.0740515111019663</v>
       </c>
       <c r="C41">
-        <v>3095.756332971764</v>
+        <v>3036.489295426308</v>
       </c>
       <c r="D41">
-        <v>4546.010517519983</v>
+        <v>4544.111535988584</v>
       </c>
       <c r="E41">
-        <v>1117.648583142529</v>
+        <v>1175.016639156586</v>
       </c>
       <c r="F41">
-        <v>2237.35418454822</v>
+        <v>2294.722240562277</v>
       </c>
       <c r="G41">
         <v>787.1</v>
@@ -4649,28 +4649,28 @@
         <v>428.91</v>
       </c>
       <c r="M41">
-        <v>160.865765869017</v>
+        <v>164.9905290964277</v>
       </c>
       <c r="N41">
-        <v>268.044234130983</v>
+        <v>263.9194709035723</v>
       </c>
       <c r="O41">
-        <v>67.01105853274575</v>
+        <v>65.97986772589309</v>
       </c>
       <c r="P41">
-        <v>201.0331755982372</v>
+        <v>197.9396031776793</v>
       </c>
       <c r="Q41">
-        <v>627.7331755982373</v>
+        <v>624.6396031776792</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08689993400642</v>
+        <v>0.08746918516994383</v>
       </c>
       <c r="T41">
-        <v>0.8011142130520633</v>
+        <v>0.8122099777757761</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.666260267888413</v>
+        <v>2.599603761191203</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0740515111019663</v>
+        <v>0.07406331246001638</v>
       </c>
       <c r="C42">
-        <v>3036.489295426308</v>
+        <v>2977.223843721935</v>
       </c>
       <c r="D42">
-        <v>4544.111535988584</v>
+        <v>4542.214140298268</v>
       </c>
       <c r="E42">
-        <v>1175.016639156586</v>
+        <v>1232.384695170643</v>
       </c>
       <c r="F42">
-        <v>2294.722240562277</v>
+        <v>2352.090296576333</v>
       </c>
       <c r="G42">
         <v>787.1</v>
@@ -4731,28 +4731,28 @@
         <v>428.91</v>
       </c>
       <c r="M42">
-        <v>164.9905290964277</v>
+        <v>169.1152923238384</v>
       </c>
       <c r="N42">
-        <v>263.9194709035723</v>
+        <v>259.7947076761616</v>
       </c>
       <c r="O42">
-        <v>65.97986772589309</v>
+        <v>64.94867691904041</v>
       </c>
       <c r="P42">
-        <v>197.9396031776793</v>
+        <v>194.8460307571212</v>
       </c>
       <c r="Q42">
-        <v>624.6396031776792</v>
+        <v>621.5460307571212</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08746918516994383</v>
+        <v>0.08805773298307862</v>
       </c>
       <c r="T42">
-        <v>0.8122099777757761</v>
+        <v>0.8236818701172419</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.599603761191203</v>
+        <v>2.536198791406052</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07406331246001638</v>
+        <v>0.07530361381806649</v>
       </c>
       <c r="C43">
-        <v>2977.223843721935</v>
+        <v>2728.905811155629</v>
       </c>
       <c r="D43">
-        <v>4542.214140298268</v>
+        <v>4351.264163746019</v>
       </c>
       <c r="E43">
-        <v>1232.384695170643</v>
+        <v>1289.7527511847</v>
       </c>
       <c r="F43">
-        <v>2352.090296576333</v>
+        <v>2409.45835259039</v>
       </c>
       <c r="G43">
         <v>787.1</v>
@@ -4813,45 +4813,45 @@
         <v>428.91</v>
       </c>
       <c r="M43">
-        <v>169.1152923238384</v>
+        <v>182.6369431263516</v>
       </c>
       <c r="N43">
-        <v>259.7947076761616</v>
+        <v>246.2730568736484</v>
       </c>
       <c r="O43">
-        <v>64.94867691904041</v>
+        <v>61.5682642184121</v>
       </c>
       <c r="P43">
-        <v>194.8460307571212</v>
+        <v>184.7047926552363</v>
       </c>
       <c r="Q43">
-        <v>621.5460307571212</v>
+        <v>611.4047926552363</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08805773298307862</v>
+        <v>0.0886665755483905</v>
       </c>
       <c r="T43">
-        <v>0.8236818701172419</v>
+        <v>0.835549344953241</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.536198791406052</v>
+        <v>2.348429581978232</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07530361381806649</v>
+        <v>0.07534466517611657</v>
       </c>
       <c r="C44">
-        <v>2728.90581115563</v>
+        <v>2665.491814120017</v>
       </c>
       <c r="D44">
-        <v>4351.264163746019</v>
+        <v>4345.218222724464</v>
       </c>
       <c r="E44">
-        <v>1289.752751184699</v>
+        <v>1347.120807198756</v>
       </c>
       <c r="F44">
-        <v>2409.45835259039</v>
+        <v>2466.826408604447</v>
       </c>
       <c r="G44">
         <v>787.1</v>
@@ -4895,28 +4895,28 @@
         <v>428.91</v>
       </c>
       <c r="M44">
-        <v>182.6369431263516</v>
+        <v>186.9854417722171</v>
       </c>
       <c r="N44">
-        <v>246.2730568736484</v>
+        <v>241.9245582277829</v>
       </c>
       <c r="O44">
-        <v>61.56826421841211</v>
+        <v>60.48113955694573</v>
       </c>
       <c r="P44">
-        <v>184.7047926552363</v>
+        <v>181.4434186708372</v>
       </c>
       <c r="Q44">
-        <v>611.4047926552363</v>
+        <v>608.1434186708373</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0886665755483905</v>
+        <v>0.08929678101073082</v>
       </c>
       <c r="T44">
-        <v>0.835549344953241</v>
+        <v>0.8478332224150644</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.348429581978232</v>
+        <v>2.293814940536878</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07534466517611657</v>
+        <v>0.07538571653416667</v>
       </c>
       <c r="C45">
-        <v>2665.491814120017</v>
+        <v>2602.094595051522</v>
       </c>
       <c r="D45">
-        <v>4345.218222724464</v>
+        <v>4339.189059670026</v>
       </c>
       <c r="E45">
-        <v>1347.120807198756</v>
+        <v>1404.488863212814</v>
       </c>
       <c r="F45">
-        <v>2466.826408604447</v>
+        <v>2524.194464618504</v>
       </c>
       <c r="G45">
         <v>787.1</v>
@@ -4977,28 +4977,28 @@
         <v>428.91</v>
       </c>
       <c r="M45">
-        <v>186.9854417722171</v>
+        <v>191.3339404180826</v>
       </c>
       <c r="N45">
-        <v>241.9245582277829</v>
+        <v>237.5760595819174</v>
       </c>
       <c r="O45">
-        <v>60.48113955694573</v>
+        <v>59.39401489547934</v>
       </c>
       <c r="P45">
-        <v>181.4434186708372</v>
+        <v>178.182044686438</v>
       </c>
       <c r="Q45">
-        <v>608.1434186708373</v>
+        <v>604.882044686438</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08929678101073082</v>
+        <v>0.08994949381101192</v>
       </c>
       <c r="T45">
-        <v>0.8478332224150644</v>
+        <v>0.860555809786239</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.293814940536878</v>
+        <v>2.241682782797403</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07538571653416667</v>
+        <v>0.07542676789221678</v>
       </c>
       <c r="C46">
-        <v>2602.094595051522</v>
+        <v>2538.714084206629</v>
       </c>
       <c r="D46">
-        <v>4339.189059670026</v>
+        <v>4333.17660483919</v>
       </c>
       <c r="E46">
-        <v>1404.488863212814</v>
+        <v>1461.856919226871</v>
       </c>
       <c r="F46">
-        <v>2524.194464618504</v>
+        <v>2581.562520632561</v>
       </c>
       <c r="G46">
         <v>787.1</v>
@@ -5059,28 +5059,28 @@
         <v>428.91</v>
       </c>
       <c r="M46">
-        <v>191.3339404180826</v>
+        <v>195.6824390639482</v>
       </c>
       <c r="N46">
-        <v>237.5760595819174</v>
+        <v>233.2275609360519</v>
       </c>
       <c r="O46">
-        <v>59.39401489547934</v>
+        <v>58.30689023401297</v>
       </c>
       <c r="P46">
-        <v>178.182044686438</v>
+        <v>174.9206707020389</v>
       </c>
       <c r="Q46">
-        <v>604.882044686438</v>
+        <v>601.6206707020389</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08994949381101192</v>
+        <v>0.0906259416222123</v>
       </c>
       <c r="T46">
-        <v>0.860555809786239</v>
+        <v>0.8737410366981833</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.241682782797403</v>
+        <v>2.19186760984635</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07542676789221678</v>
+        <v>0.07546781925026685</v>
       </c>
       <c r="C47">
-        <v>2538.714084206629</v>
+        <v>2475.350212227842</v>
       </c>
       <c r="D47">
-        <v>4333.17660483919</v>
+        <v>4327.18078887446</v>
       </c>
       <c r="E47">
-        <v>1461.856919226871</v>
+        <v>1519.224975240928</v>
       </c>
       <c r="F47">
-        <v>2581.562520632561</v>
+        <v>2638.930576646618</v>
       </c>
       <c r="G47">
         <v>787.1</v>
@@ -5141,28 +5141,28 @@
         <v>428.91</v>
       </c>
       <c r="M47">
-        <v>195.6824390639482</v>
+        <v>200.0309377098137</v>
       </c>
       <c r="N47">
-        <v>233.2275609360519</v>
+        <v>228.8790622901863</v>
       </c>
       <c r="O47">
-        <v>58.30689023401297</v>
+        <v>57.21976557254659</v>
       </c>
       <c r="P47">
-        <v>174.9206707020389</v>
+        <v>171.6592967176398</v>
       </c>
       <c r="Q47">
-        <v>601.6206707020389</v>
+        <v>598.3592967176397</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0906259416222123</v>
+        <v>0.09132744305604973</v>
       </c>
       <c r="T47">
-        <v>0.8737410366981833</v>
+        <v>0.8874146053476072</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.19186760984635</v>
+        <v>2.144218313980125</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07546781925026685</v>
+        <v>0.07550887060831696</v>
       </c>
       <c r="C48">
-        <v>2475.350212227842</v>
+        <v>2412.002910141001</v>
       </c>
       <c r="D48">
-        <v>4327.18078887446</v>
+        <v>4321.201542801676</v>
       </c>
       <c r="E48">
-        <v>1519.224975240928</v>
+        <v>1576.593031254985</v>
       </c>
       <c r="F48">
-        <v>2638.930576646618</v>
+        <v>2696.298632660675</v>
       </c>
       <c r="G48">
         <v>787.1</v>
@@ -5223,28 +5223,28 @@
         <v>428.91</v>
       </c>
       <c r="M48">
-        <v>200.0309377098137</v>
+        <v>204.3794363556792</v>
       </c>
       <c r="N48">
-        <v>228.8790622901863</v>
+        <v>224.5305636443208</v>
       </c>
       <c r="O48">
-        <v>57.21976557254659</v>
+        <v>56.13264091108021</v>
       </c>
       <c r="P48">
-        <v>171.6592967176398</v>
+        <v>168.3979227332406</v>
       </c>
       <c r="Q48">
-        <v>598.3592967176397</v>
+        <v>595.0979227332406</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09132744305604973</v>
+        <v>0.09205541624210745</v>
       </c>
       <c r="T48">
-        <v>0.8874146053476072</v>
+        <v>0.9016041577196507</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.144218313980125</v>
+        <v>2.098596647725229</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07550887060831696</v>
+        <v>0.07554992196636705</v>
       </c>
       <c r="C49">
-        <v>2412.002910141001</v>
+        <v>2348.672109352666</v>
       </c>
       <c r="D49">
-        <v>4321.201542801676</v>
+        <v>4315.238798027398</v>
       </c>
       <c r="E49">
-        <v>1576.593031254985</v>
+        <v>1633.961087269042</v>
       </c>
       <c r="F49">
-        <v>2696.298632660675</v>
+        <v>2753.666688674732</v>
       </c>
       <c r="G49">
         <v>787.1</v>
@@ -5305,28 +5305,28 @@
         <v>428.91</v>
       </c>
       <c r="M49">
-        <v>204.3794363556792</v>
+        <v>208.7279350015447</v>
       </c>
       <c r="N49">
-        <v>224.5305636443208</v>
+        <v>220.1820649984553</v>
       </c>
       <c r="O49">
-        <v>56.13264091108021</v>
+        <v>55.04551624961383</v>
       </c>
       <c r="P49">
-        <v>168.3979227332406</v>
+        <v>165.1365487488415</v>
       </c>
       <c r="Q49">
-        <v>595.0979227332406</v>
+        <v>591.8365487488414</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09205541624210745</v>
+        <v>0.09281138839685971</v>
       </c>
       <c r="T49">
-        <v>0.9016041577196507</v>
+        <v>0.9163394621060038</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.098596647725229</v>
+        <v>2.054875884230952</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07554992196636705</v>
+        <v>0.07559097332441714</v>
       </c>
       <c r="C50">
-        <v>2348.672109352667</v>
+        <v>2285.357741647468</v>
       </c>
       <c r="D50">
-        <v>4315.238798027398</v>
+        <v>4309.292486336256</v>
       </c>
       <c r="E50">
-        <v>1633.961087269041</v>
+        <v>1691.329143283098</v>
       </c>
       <c r="F50">
-        <v>2753.666688674732</v>
+        <v>2811.034744688789</v>
       </c>
       <c r="G50">
         <v>787.1</v>
@@ -5387,28 +5387,28 @@
         <v>428.91</v>
       </c>
       <c r="M50">
-        <v>208.7279350015447</v>
+        <v>213.0764336474102</v>
       </c>
       <c r="N50">
-        <v>220.1820649984554</v>
+        <v>215.8335663525898</v>
       </c>
       <c r="O50">
-        <v>55.04551624961384</v>
+        <v>53.95839158814746</v>
       </c>
       <c r="P50">
-        <v>165.1365487488415</v>
+        <v>161.8751747644424</v>
       </c>
       <c r="Q50">
-        <v>591.8365487488416</v>
+        <v>588.5751747644424</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09281138839685971</v>
+        <v>0.09359700651846498</v>
       </c>
       <c r="T50">
-        <v>0.9163394621060038</v>
+        <v>0.9316526215663313</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.054875884230953</v>
+        <v>2.012939641695628</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07559097332441714</v>
+        <v>0.08095702468246724</v>
       </c>
       <c r="C51">
-        <v>2285.357741647468</v>
+        <v>1570.258122527855</v>
       </c>
       <c r="D51">
-        <v>4309.292486336256</v>
+        <v>3651.560923230701</v>
       </c>
       <c r="E51">
-        <v>1691.329143283098</v>
+        <v>1748.697199297155</v>
       </c>
       <c r="F51">
-        <v>2811.034744688789</v>
+        <v>2868.402800702846</v>
       </c>
       <c r="G51">
         <v>787.1</v>
@@ -5469,45 +5469,45 @@
         <v>428.91</v>
       </c>
       <c r="M51">
-        <v>213.0764336474102</v>
+        <v>258.1562520632561</v>
       </c>
       <c r="N51">
-        <v>215.8335663525898</v>
+        <v>170.7537479367439</v>
       </c>
       <c r="O51">
-        <v>53.95839158814746</v>
+        <v>42.68843698418598</v>
       </c>
       <c r="P51">
-        <v>161.8751747644424</v>
+        <v>128.065310952558</v>
       </c>
       <c r="Q51">
-        <v>588.5751747644424</v>
+        <v>554.7653109525579</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09359700651846498</v>
+        <v>0.09441404936493447</v>
       </c>
       <c r="T51">
-        <v>0.9316526215663313</v>
+        <v>0.9475783074050721</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.012939641695628</v>
+        <v>1.661435648263534</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08095702468246724</v>
+        <v>0.08110457604051732</v>
       </c>
       <c r="C52">
-        <v>1570.258122527855</v>
+        <v>1497.628793510351</v>
       </c>
       <c r="D52">
-        <v>3651.560923230701</v>
+        <v>3636.299650227254</v>
       </c>
       <c r="E52">
-        <v>1748.697199297155</v>
+        <v>1806.065255311212</v>
       </c>
       <c r="F52">
-        <v>2868.402800702846</v>
+        <v>2925.770856716902</v>
       </c>
       <c r="G52">
         <v>787.1</v>
@@ -5551,28 +5551,28 @@
         <v>428.91</v>
       </c>
       <c r="M52">
-        <v>258.1562520632561</v>
+        <v>263.3193771045212</v>
       </c>
       <c r="N52">
-        <v>170.7537479367439</v>
+        <v>165.5906228954788</v>
       </c>
       <c r="O52">
-        <v>42.68843698418598</v>
+        <v>41.3976557238697</v>
       </c>
       <c r="P52">
-        <v>128.065310952558</v>
+        <v>124.1929671716091</v>
       </c>
       <c r="Q52">
-        <v>554.7653109525579</v>
+        <v>550.8929671716091</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09441404936493447</v>
+        <v>0.09526444089901495</v>
       </c>
       <c r="T52">
-        <v>0.9475783074050721</v>
+        <v>0.9641540212372308</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.661435648263534</v>
+        <v>1.628858478689739</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08110457604051732</v>
+        <v>0.08125212739856744</v>
       </c>
       <c r="C53">
-        <v>1497.628793510351</v>
+        <v>1425.12649898823</v>
       </c>
       <c r="D53">
-        <v>3636.299650227254</v>
+        <v>3621.16541171919</v>
       </c>
       <c r="E53">
-        <v>1806.065255311212</v>
+        <v>1863.433311325269</v>
       </c>
       <c r="F53">
-        <v>2925.770856716902</v>
+        <v>2983.138912730959</v>
       </c>
       <c r="G53">
         <v>787.1</v>
@@ -5633,28 +5633,28 @@
         <v>428.91</v>
       </c>
       <c r="M53">
-        <v>263.3193771045212</v>
+        <v>268.4825021457863</v>
       </c>
       <c r="N53">
-        <v>165.5906228954788</v>
+        <v>160.4274978542137</v>
       </c>
       <c r="O53">
-        <v>41.3976557238697</v>
+        <v>40.10687446355342</v>
       </c>
       <c r="P53">
-        <v>124.1929671716091</v>
+        <v>120.3206233906603</v>
       </c>
       <c r="Q53">
-        <v>550.8929671716091</v>
+        <v>547.0206233906603</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09526444089901495</v>
+        <v>0.09615026541368213</v>
       </c>
       <c r="T53">
-        <v>0.9641540212372308</v>
+        <v>0.9814203898123961</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.628858478689739</v>
+        <v>1.597534277176474</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08125212739856744</v>
+        <v>0.08139967875661752</v>
       </c>
       <c r="C54">
-        <v>1425.12649898823</v>
+        <v>1352.749659387219</v>
       </c>
       <c r="D54">
-        <v>3621.16541171919</v>
+        <v>3606.156628132235</v>
       </c>
       <c r="E54">
-        <v>1863.433311325269</v>
+        <v>1920.801367339326</v>
       </c>
       <c r="F54">
-        <v>2983.138912730959</v>
+        <v>3040.506968745016</v>
       </c>
       <c r="G54">
         <v>787.1</v>
@@ -5715,28 +5715,28 @@
         <v>428.91</v>
       </c>
       <c r="M54">
-        <v>268.4825021457863</v>
+        <v>273.6456271870514</v>
       </c>
       <c r="N54">
-        <v>160.4274978542137</v>
+        <v>155.2643728129486</v>
       </c>
       <c r="O54">
-        <v>40.10687446355342</v>
+        <v>38.81609320323714</v>
       </c>
       <c r="P54">
-        <v>120.3206233906603</v>
+        <v>116.4482796097114</v>
       </c>
       <c r="Q54">
-        <v>547.0206233906603</v>
+        <v>543.1482796097114</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09615026541368213</v>
+        <v>0.0970737845885479</v>
       </c>
       <c r="T54">
-        <v>0.9814203898123961</v>
+        <v>0.9994214974758664</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.597534277176474</v>
+        <v>1.567392121003333</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08139967875661752</v>
+        <v>0.08154723011466761</v>
       </c>
       <c r="C55">
-        <v>1352.749659387219</v>
+        <v>1280.496721212631</v>
       </c>
       <c r="D55">
-        <v>3606.156628132235</v>
+        <v>3591.271745971704</v>
       </c>
       <c r="E55">
-        <v>1920.801367339326</v>
+        <v>1978.169423353383</v>
       </c>
       <c r="F55">
-        <v>3040.506968745016</v>
+        <v>3097.875024759073</v>
       </c>
       <c r="G55">
         <v>787.1</v>
@@ -5797,28 +5797,28 @@
         <v>428.91</v>
       </c>
       <c r="M55">
-        <v>273.6456271870514</v>
+        <v>278.8087522283166</v>
       </c>
       <c r="N55">
-        <v>155.2643728129486</v>
+        <v>150.1012477716835</v>
       </c>
       <c r="O55">
-        <v>38.81609320323714</v>
+        <v>37.52531194292087</v>
       </c>
       <c r="P55">
-        <v>116.4482796097114</v>
+        <v>112.5759358287626</v>
       </c>
       <c r="Q55">
-        <v>543.1482796097114</v>
+        <v>539.2759358287626</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.0970737845885479</v>
+        <v>0.09803745677101654</v>
       </c>
       <c r="T55">
-        <v>0.9994214974758664</v>
+        <v>1.01820526199427</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.567392121003333</v>
+        <v>1.538366340984753</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08154723011466761</v>
+        <v>0.08169478147271769</v>
       </c>
       <c r="C56">
-        <v>1280.496721212631</v>
+        <v>1208.366156513355</v>
       </c>
       <c r="D56">
-        <v>3591.271745971704</v>
+        <v>3576.509237286485</v>
       </c>
       <c r="E56">
-        <v>1978.169423353383</v>
+        <v>2035.53747936744</v>
       </c>
       <c r="F56">
-        <v>3097.875024759073</v>
+        <v>3155.24308077313</v>
       </c>
       <c r="G56">
         <v>787.1</v>
@@ -5879,28 +5879,28 @@
         <v>428.91</v>
       </c>
       <c r="M56">
-        <v>278.8087522283166</v>
+        <v>283.9718772695817</v>
       </c>
       <c r="N56">
-        <v>150.1012477716835</v>
+        <v>144.9381227304183</v>
       </c>
       <c r="O56">
-        <v>37.52531194292087</v>
+        <v>36.23453068260457</v>
       </c>
       <c r="P56">
-        <v>112.5759358287626</v>
+        <v>108.7035920478137</v>
       </c>
       <c r="Q56">
-        <v>539.2759358287626</v>
+        <v>535.4035920478137</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09803745677101654</v>
+        <v>0.09904395882826156</v>
       </c>
       <c r="T56">
-        <v>1.01820526199427</v>
+        <v>1.03782386049127</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.538366340984753</v>
+        <v>1.510396043875939</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08169478147271769</v>
+        <v>0.1079113164824624</v>
       </c>
       <c r="C57">
-        <v>1208.366156513355</v>
+        <v>-358.6089235036702</v>
       </c>
       <c r="D57">
-        <v>3576.509237286485</v>
+        <v>2066.902213283517</v>
       </c>
       <c r="E57">
-        <v>2035.53747936744</v>
+        <v>2092.905535381497</v>
       </c>
       <c r="F57">
-        <v>3155.24308077313</v>
+        <v>3212.611136787187</v>
       </c>
       <c r="G57">
         <v>787.1</v>
@@ -5961,45 +5961,45 @@
         <v>428.91</v>
       </c>
       <c r="M57">
-        <v>283.9718772695817</v>
+        <v>471.6113148803591</v>
       </c>
       <c r="N57">
-        <v>144.9381227304183</v>
+        <v>-42.70131488035912</v>
       </c>
       <c r="O57">
-        <v>36.23453068260457</v>
+        <v>-10.67532872008978</v>
       </c>
       <c r="P57">
-        <v>108.7035920478137</v>
+        <v>-32.02598616026934</v>
       </c>
       <c r="Q57">
-        <v>535.4035920478137</v>
+        <v>394.6740138397307</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09904395882826156</v>
+        <v>0.1008965171032436</v>
       </c>
       <c r="T57">
-        <v>1.03782386049127</v>
+        <v>1.073933669435574</v>
       </c>
       <c r="U57">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.25</v>
+        <v>0.2273641378328721</v>
       </c>
       <c r="W57">
-        <v>0.0675</v>
+        <v>0.1134229445661344</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.510396043875939</v>
+        <v>0.9094565513314883</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1079113164824624</v>
+        <v>0.1089213164824624</v>
       </c>
       <c r="C58">
-        <v>-358.6089235036702</v>
+        <v>-449.0493447938284</v>
       </c>
       <c r="D58">
-        <v>2066.902213283517</v>
+        <v>2033.829848007416</v>
       </c>
       <c r="E58">
-        <v>2092.905535381497</v>
+        <v>2150.273591395554</v>
       </c>
       <c r="F58">
-        <v>3212.611136787187</v>
+        <v>3269.979192801244</v>
       </c>
       <c r="G58">
         <v>787.1</v>
@@ -6043,37 +6043,37 @@
         <v>428.91</v>
       </c>
       <c r="M58">
-        <v>471.6113148803591</v>
+        <v>480.0329455032227</v>
       </c>
       <c r="N58">
-        <v>-42.70131488035912</v>
+        <v>-51.12294550322264</v>
       </c>
       <c r="O58">
-        <v>-10.67532872008978</v>
+        <v>-12.78073637580566</v>
       </c>
       <c r="P58">
-        <v>-32.02598616026934</v>
+        <v>-38.34220912741698</v>
       </c>
       <c r="Q58">
-        <v>394.6740138397307</v>
+        <v>388.357790872583</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1008965171032436</v>
+        <v>0.1021778314544819</v>
       </c>
       <c r="T58">
-        <v>1.073933669435574</v>
+        <v>1.098908871050355</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2273641378328721</v>
+        <v>0.2233752933094884</v>
       </c>
       <c r="W58">
-        <v>0.1134229445661344</v>
+        <v>0.1140085069421671</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9094565513314883</v>
+        <v>0.8935011732379534</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1089213164824624</v>
+        <v>0.1099313164824625</v>
       </c>
       <c r="C59">
-        <v>-449.0493447938284</v>
+        <v>-538.4480569546254</v>
       </c>
       <c r="D59">
-        <v>2033.829848007416</v>
+        <v>2001.799191860676</v>
       </c>
       <c r="E59">
-        <v>2150.273591395554</v>
+        <v>2207.64164740961</v>
       </c>
       <c r="F59">
-        <v>3269.979192801244</v>
+        <v>3327.347248815301</v>
       </c>
       <c r="G59">
         <v>787.1</v>
@@ -6125,37 +6125,37 @@
         <v>428.91</v>
       </c>
       <c r="M59">
-        <v>480.0329455032227</v>
+        <v>488.4545761260862</v>
       </c>
       <c r="N59">
-        <v>-51.12294550322264</v>
+        <v>-59.54457612608621</v>
       </c>
       <c r="O59">
-        <v>-12.78073637580566</v>
+        <v>-14.88614403152155</v>
       </c>
       <c r="P59">
-        <v>-38.34220912741698</v>
+        <v>-44.65843209456466</v>
       </c>
       <c r="Q59">
-        <v>388.357790872583</v>
+        <v>382.0415679054353</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1021778314544819</v>
+        <v>0.1035201607748266</v>
       </c>
       <c r="T59">
-        <v>1.098908871050355</v>
+        <v>1.125073367980125</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2233752933094884</v>
+        <v>0.2195239951489799</v>
       </c>
       <c r="W59">
-        <v>0.1140085069421671</v>
+        <v>0.1145738775121298</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8935011732379534</v>
+        <v>0.8780959805959198</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1099313164824624</v>
+        <v>0.1109413164824624</v>
       </c>
       <c r="C60">
-        <v>-538.4480569546236</v>
+        <v>-626.8535143132426</v>
       </c>
       <c r="D60">
-        <v>2001.799191860677</v>
+        <v>1970.761790516115</v>
       </c>
       <c r="E60">
-        <v>2207.64164740961</v>
+        <v>2265.009703423667</v>
       </c>
       <c r="F60">
-        <v>3327.347248815301</v>
+        <v>3384.715304829358</v>
       </c>
       <c r="G60">
         <v>787.1</v>
@@ -6207,37 +6207,37 @@
         <v>428.91</v>
       </c>
       <c r="M60">
-        <v>488.4545761260862</v>
+        <v>496.8762067489498</v>
       </c>
       <c r="N60">
-        <v>-59.54457612608616</v>
+        <v>-67.96620674894973</v>
       </c>
       <c r="O60">
-        <v>-14.88614403152154</v>
+        <v>-16.99155168723743</v>
       </c>
       <c r="P60">
-        <v>-44.65843209456462</v>
+        <v>-50.9746550617123</v>
       </c>
       <c r="Q60">
-        <v>382.0415679054354</v>
+        <v>375.7253449382877</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1035201607748266</v>
+        <v>0.1049279695742126</v>
       </c>
       <c r="T60">
-        <v>1.125073367980125</v>
+        <v>1.152514181833298</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.21952399514898</v>
+        <v>0.2158032494684888</v>
       </c>
       <c r="W60">
-        <v>0.1145738775121297</v>
+        <v>0.1151200829780259</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8780959805959199</v>
+        <v>0.8632129978739551</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1109413164824624</v>
+        <v>0.1119513164824624</v>
       </c>
       <c r="C61">
-        <v>-626.8535143132426</v>
+        <v>-714.3112119892148</v>
       </c>
       <c r="D61">
-        <v>1970.761790516115</v>
+        <v>1940.6721488542</v>
       </c>
       <c r="E61">
-        <v>2265.009703423667</v>
+        <v>2322.377759437724</v>
       </c>
       <c r="F61">
-        <v>3384.715304829358</v>
+        <v>3442.083360843415</v>
       </c>
       <c r="G61">
         <v>787.1</v>
@@ -6289,37 +6289,37 @@
         <v>428.91</v>
       </c>
       <c r="M61">
-        <v>496.8762067489498</v>
+        <v>505.2978373718133</v>
       </c>
       <c r="N61">
-        <v>-67.96620674894973</v>
+        <v>-76.3878373718133</v>
       </c>
       <c r="O61">
-        <v>-16.99155168723743</v>
+        <v>-19.09695934295333</v>
       </c>
       <c r="P61">
-        <v>-50.9746550617123</v>
+        <v>-57.29087802885998</v>
       </c>
       <c r="Q61">
-        <v>375.7253449382877</v>
+        <v>369.40912197114</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1049279695742126</v>
+        <v>0.106406168813568</v>
       </c>
       <c r="T61">
-        <v>1.152514181833298</v>
+        <v>1.181327036379131</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2158032494684888</v>
+        <v>0.212206528644014</v>
       </c>
       <c r="W61">
-        <v>0.1151200829780259</v>
+        <v>0.1156480815950588</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8632129978739551</v>
+        <v>0.8488261145760558</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1119513164824624</v>
+        <v>0.1129613164824624</v>
       </c>
       <c r="C62">
-        <v>-714.3112119892148</v>
+        <v>-800.863908403443</v>
       </c>
       <c r="D62">
-        <v>1940.6721488542</v>
+        <v>1911.487508454028</v>
       </c>
       <c r="E62">
-        <v>2322.377759437724</v>
+        <v>2379.745815451781</v>
       </c>
       <c r="F62">
-        <v>3442.083360843415</v>
+        <v>3499.451416857471</v>
       </c>
       <c r="G62">
         <v>787.1</v>
@@ -6371,37 +6371,37 @@
         <v>428.91</v>
       </c>
       <c r="M62">
-        <v>505.2978373718133</v>
+        <v>513.7194679946768</v>
       </c>
       <c r="N62">
-        <v>-76.3878373718133</v>
+        <v>-84.80946799467682</v>
       </c>
       <c r="O62">
-        <v>-19.09695934295333</v>
+        <v>-21.20236699866921</v>
       </c>
       <c r="P62">
-        <v>-57.29087802885998</v>
+        <v>-63.60710099600762</v>
       </c>
       <c r="Q62">
-        <v>369.40912197114</v>
+        <v>363.0928990039924</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.106406168813568</v>
+        <v>0.107960173142121</v>
       </c>
       <c r="T62">
-        <v>1.181327036379131</v>
+        <v>1.211617473209365</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.212206528644014</v>
+        <v>0.2087277330924728</v>
       </c>
       <c r="W62">
-        <v>0.1156480815950588</v>
+        <v>0.116158768782025</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8488261145760558</v>
+        <v>0.834910932369891</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1129613164824624</v>
+        <v>0.1139713164824624</v>
       </c>
       <c r="C63">
-        <v>-800.863908403443</v>
+        <v>-886.5518280075662</v>
       </c>
       <c r="D63">
-        <v>1911.487508454028</v>
+        <v>1883.167644863962</v>
       </c>
       <c r="E63">
-        <v>2379.745815451781</v>
+        <v>2437.113871465838</v>
       </c>
       <c r="F63">
-        <v>3499.451416857471</v>
+        <v>3556.819472871528</v>
       </c>
       <c r="G63">
         <v>787.1</v>
@@ -6453,37 +6453,37 @@
         <v>428.91</v>
       </c>
       <c r="M63">
-        <v>513.7194679946768</v>
+        <v>522.1410986175405</v>
       </c>
       <c r="N63">
-        <v>-84.80946799467682</v>
+        <v>-93.23109861754045</v>
       </c>
       <c r="O63">
-        <v>-21.20236699866921</v>
+        <v>-23.30777465438511</v>
       </c>
       <c r="P63">
-        <v>-63.60710099600762</v>
+        <v>-69.92332396315534</v>
       </c>
       <c r="Q63">
-        <v>363.0928990039924</v>
+        <v>356.7766760368447</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.107960173142121</v>
+        <v>0.1095959671721768</v>
       </c>
       <c r="T63">
-        <v>1.211617473209365</v>
+        <v>1.24350214355698</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2087277330924728</v>
+        <v>0.2053611567522715</v>
       </c>
       <c r="W63">
-        <v>0.116158768782025</v>
+        <v>0.1166529821887665</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.834910932369891</v>
+        <v>0.8214446270090862</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1139713164824624</v>
+        <v>0.1149813164824624</v>
       </c>
       <c r="C64">
-        <v>-886.5518280075662</v>
+        <v>-971.4128462550711</v>
       </c>
       <c r="D64">
-        <v>1883.167644863962</v>
+        <v>1855.674682630514</v>
       </c>
       <c r="E64">
-        <v>2437.113871465838</v>
+        <v>2494.481927479895</v>
       </c>
       <c r="F64">
-        <v>3556.819472871528</v>
+        <v>3614.187528885585</v>
       </c>
       <c r="G64">
         <v>787.1</v>
@@ -6535,37 +6535,37 @@
         <v>428.91</v>
       </c>
       <c r="M64">
-        <v>522.1410986175405</v>
+        <v>530.562729240404</v>
       </c>
       <c r="N64">
-        <v>-93.23109861754045</v>
+        <v>-101.652729240404</v>
       </c>
       <c r="O64">
-        <v>-23.30777465438511</v>
+        <v>-25.41318231010099</v>
       </c>
       <c r="P64">
-        <v>-69.92332396315534</v>
+        <v>-76.23954693030298</v>
       </c>
       <c r="Q64">
-        <v>356.7766760368447</v>
+        <v>350.460453069697</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1095959671721768</v>
+        <v>0.1113201825011546</v>
       </c>
       <c r="T64">
-        <v>1.24350214355698</v>
+        <v>1.277110309599061</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2053611567522715</v>
+        <v>0.2021014558514418</v>
       </c>
       <c r="W64">
-        <v>0.1166529821887665</v>
+        <v>0.1171315062810084</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8214446270090862</v>
+        <v>0.8084058234057674</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1149813164824624</v>
+        <v>0.15150249885171</v>
       </c>
       <c r="C65">
-        <v>-971.4128462550711</v>
+        <v>-1669.933516810636</v>
       </c>
       <c r="D65">
-        <v>1855.674682630514</v>
+        <v>1214.522068089006</v>
       </c>
       <c r="E65">
-        <v>2494.481927479895</v>
+        <v>2551.849983493952</v>
       </c>
       <c r="F65">
-        <v>3614.187528885585</v>
+        <v>3671.555584899642</v>
       </c>
       <c r="G65">
         <v>787.1</v>
@@ -6617,45 +6617,45 @@
         <v>428.91</v>
       </c>
       <c r="M65">
-        <v>530.562729240404</v>
+        <v>737.2483614478482</v>
       </c>
       <c r="N65">
-        <v>-101.652729240404</v>
+        <v>-308.3383614478482</v>
       </c>
       <c r="O65">
-        <v>-25.41318231010099</v>
+        <v>-77.08459036196204</v>
       </c>
       <c r="P65">
-        <v>-76.23954693030298</v>
+        <v>-231.2537710858861</v>
       </c>
       <c r="Q65">
-        <v>350.460453069697</v>
+        <v>195.4462289141139</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1113201825011546</v>
+        <v>0.115782360818541</v>
       </c>
       <c r="T65">
-        <v>1.277110309599061</v>
+        <v>1.364086470453056</v>
       </c>
       <c r="U65">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.2021014558514418</v>
+        <v>0.1454428461386077</v>
       </c>
       <c r="W65">
-        <v>0.1171315062810084</v>
+        <v>0.1715950764953676</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8084058234057674</v>
+        <v>0.5817713845544308</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.15150249885171</v>
+        <v>0.15305249885171</v>
       </c>
       <c r="C66">
-        <v>-1669.933516810636</v>
+        <v>-1744.853697257158</v>
       </c>
       <c r="D66">
-        <v>1214.522068089006</v>
+        <v>1196.969943656541</v>
       </c>
       <c r="E66">
-        <v>2551.849983493952</v>
+        <v>2609.218039508009</v>
       </c>
       <c r="F66">
-        <v>3671.555584899642</v>
+        <v>3728.923640913699</v>
       </c>
       <c r="G66">
         <v>787.1</v>
@@ -6699,37 +6699,37 @@
         <v>428.91</v>
       </c>
       <c r="M66">
-        <v>737.2483614478482</v>
+        <v>748.7678670954708</v>
       </c>
       <c r="N66">
-        <v>-308.3383614478482</v>
+        <v>-319.8578670954708</v>
       </c>
       <c r="O66">
-        <v>-77.08459036196204</v>
+        <v>-79.9644667738677</v>
       </c>
       <c r="P66">
-        <v>-231.2537710858861</v>
+        <v>-239.8934003216031</v>
       </c>
       <c r="Q66">
-        <v>195.4462289141139</v>
+        <v>186.8065996783969</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.115782360818541</v>
+        <v>0.1177818568419279</v>
       </c>
       <c r="T66">
-        <v>1.364086470453056</v>
+        <v>1.403060369608858</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1454428461386077</v>
+        <v>0.1432052638903214</v>
       </c>
       <c r="W66">
-        <v>0.1715950764953676</v>
+        <v>0.1720443830108235</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5817713845544308</v>
+        <v>0.5728210555612856</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.15305249885171</v>
+        <v>0.15460249885171</v>
       </c>
       <c r="C67">
-        <v>-1744.853697257158</v>
+        <v>-1819.273782702968</v>
       </c>
       <c r="D67">
-        <v>1196.969943656541</v>
+        <v>1179.917914224788</v>
       </c>
       <c r="E67">
-        <v>2609.218039508009</v>
+        <v>2666.586095522066</v>
       </c>
       <c r="F67">
-        <v>3728.923640913699</v>
+        <v>3786.291696927756</v>
       </c>
       <c r="G67">
         <v>787.1</v>
@@ -6781,37 +6781,37 @@
         <v>428.91</v>
       </c>
       <c r="M67">
-        <v>748.7678670954708</v>
+        <v>760.2873727430934</v>
       </c>
       <c r="N67">
-        <v>-319.8578670954708</v>
+        <v>-331.3773727430934</v>
       </c>
       <c r="O67">
-        <v>-79.9644667738677</v>
+        <v>-82.84434318577335</v>
       </c>
       <c r="P67">
-        <v>-239.8934003216031</v>
+        <v>-248.53302955732</v>
       </c>
       <c r="Q67">
-        <v>186.8065996783969</v>
+        <v>178.1669704426799</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1177818568419279</v>
+        <v>0.1198989702784551</v>
       </c>
       <c r="T67">
-        <v>1.403060369608858</v>
+        <v>1.444326851067942</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1432052638903214</v>
+        <v>0.1410354871647105</v>
       </c>
       <c r="W67">
-        <v>0.1720443830108235</v>
+        <v>0.1724800741773261</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5728210555612856</v>
+        <v>0.5641419486588419</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.15460249885171</v>
+        <v>0.15615249885171</v>
       </c>
       <c r="C68">
-        <v>-1819.273782702968</v>
+        <v>-1893.214845998953</v>
       </c>
       <c r="D68">
-        <v>1179.917914224788</v>
+        <v>1163.34490694286</v>
       </c>
       <c r="E68">
-        <v>2666.586095522066</v>
+        <v>2723.954151536122</v>
       </c>
       <c r="F68">
-        <v>3786.291696927756</v>
+        <v>3843.659752941813</v>
       </c>
       <c r="G68">
         <v>787.1</v>
@@ -6863,37 +6863,37 @@
         <v>428.91</v>
       </c>
       <c r="M68">
-        <v>760.2873727430934</v>
+        <v>771.8068783907161</v>
       </c>
       <c r="N68">
-        <v>-331.3773727430934</v>
+        <v>-342.896878390716</v>
       </c>
       <c r="O68">
-        <v>-82.84434318577335</v>
+        <v>-85.72421959767901</v>
       </c>
       <c r="P68">
-        <v>-248.53302955732</v>
+        <v>-257.172658793037</v>
       </c>
       <c r="Q68">
-        <v>178.1669704426799</v>
+        <v>169.5273412069629</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1198989702784551</v>
+        <v>0.1221443936202265</v>
       </c>
       <c r="T68">
-        <v>1.444326851067942</v>
+        <v>1.488094331403334</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1410354871647105</v>
+        <v>0.1389304798935954</v>
       </c>
       <c r="W68">
-        <v>0.1724800741773261</v>
+        <v>0.172902759637366</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5641419486588419</v>
+        <v>0.5557219195743817</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.15615249885171</v>
+        <v>0.15770249885171</v>
       </c>
       <c r="C69">
-        <v>-1893.214845998953</v>
+        <v>-1966.69679244678</v>
       </c>
       <c r="D69">
-        <v>1163.34490694286</v>
+        <v>1147.23101650909</v>
       </c>
       <c r="E69">
-        <v>2723.954151536122</v>
+        <v>2781.32220755018</v>
       </c>
       <c r="F69">
-        <v>3843.659752941813</v>
+        <v>3901.02780895587</v>
       </c>
       <c r="G69">
         <v>787.1</v>
@@ -6945,37 +6945,37 @@
         <v>428.91</v>
       </c>
       <c r="M69">
-        <v>771.8068783907161</v>
+        <v>783.3263840383387</v>
       </c>
       <c r="N69">
-        <v>-342.896878390716</v>
+        <v>-354.4163840383387</v>
       </c>
       <c r="O69">
-        <v>-85.72421959767901</v>
+        <v>-88.60409600958467</v>
       </c>
       <c r="P69">
-        <v>-257.172658793037</v>
+        <v>-265.812288028754</v>
       </c>
       <c r="Q69">
-        <v>169.5273412069629</v>
+        <v>160.887711971246</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1221443936202265</v>
+        <v>0.1245301559208586</v>
       </c>
       <c r="T69">
-        <v>1.488094331403334</v>
+        <v>1.534597279259688</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1389304798935954</v>
+        <v>0.1368873846010425</v>
       </c>
       <c r="W69">
-        <v>0.172902759637366</v>
+        <v>0.1733130131721107</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5557219195743817</v>
+        <v>0.5475495384041701</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.15770249885171</v>
+        <v>0.15925249885171</v>
       </c>
       <c r="C70">
-        <v>-1966.69679244678</v>
+        <v>-2039.738439554792</v>
       </c>
       <c r="D70">
-        <v>1147.23101650909</v>
+        <v>1131.557425415136</v>
       </c>
       <c r="E70">
-        <v>2781.32220755018</v>
+        <v>2838.690263564236</v>
       </c>
       <c r="F70">
-        <v>3901.02780895587</v>
+        <v>3958.395864969927</v>
       </c>
       <c r="G70">
         <v>787.1</v>
@@ -7027,37 +7027,37 @@
         <v>428.91</v>
       </c>
       <c r="M70">
-        <v>783.3263840383387</v>
+        <v>794.8458896859614</v>
       </c>
       <c r="N70">
-        <v>-354.4163840383387</v>
+        <v>-365.9358896859614</v>
       </c>
       <c r="O70">
-        <v>-88.60409600958467</v>
+        <v>-91.48397242149035</v>
       </c>
       <c r="P70">
-        <v>-265.812288028754</v>
+        <v>-274.451917264471</v>
       </c>
       <c r="Q70">
-        <v>160.887711971246</v>
+        <v>152.248082735529</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1245301559208586</v>
+        <v>0.1270698383699186</v>
       </c>
       <c r="T70">
-        <v>1.534597279259688</v>
+        <v>1.584100417300323</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1368873846010425</v>
+        <v>0.134903509461897</v>
       </c>
       <c r="W70">
-        <v>0.1733130131721107</v>
+        <v>0.1737113753000511</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5475495384041701</v>
+        <v>0.5396140378475878</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.15925249885171</v>
+        <v>0.16080249885171</v>
       </c>
       <c r="C71">
-        <v>-2039.738439554792</v>
+        <v>-2112.357590344232</v>
       </c>
       <c r="D71">
-        <v>1131.557425415136</v>
+        <v>1116.306330639751</v>
       </c>
       <c r="E71">
-        <v>2838.690263564236</v>
+        <v>2896.058319578294</v>
       </c>
       <c r="F71">
-        <v>3958.395864969927</v>
+        <v>4015.763920983984</v>
       </c>
       <c r="G71">
         <v>787.1</v>
@@ -7109,37 +7109,37 @@
         <v>428.91</v>
       </c>
       <c r="M71">
-        <v>794.8458896859614</v>
+        <v>806.365395333584</v>
       </c>
       <c r="N71">
-        <v>-365.9358896859614</v>
+        <v>-377.455395333584</v>
       </c>
       <c r="O71">
-        <v>-91.48397242149035</v>
+        <v>-94.36384883339601</v>
       </c>
       <c r="P71">
-        <v>-274.451917264471</v>
+        <v>-283.091546500188</v>
       </c>
       <c r="Q71">
-        <v>152.248082735529</v>
+        <v>143.608453499812</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1270698383699186</v>
+        <v>0.1297788329822492</v>
       </c>
       <c r="T71">
-        <v>1.584100417300323</v>
+        <v>1.636903764543667</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.134903509461897</v>
+        <v>0.1329763164695842</v>
       </c>
       <c r="W71">
-        <v>0.1737113753000511</v>
+        <v>0.1740983556529075</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5396140378475878</v>
+        <v>0.5319052658783365</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.16080249885171</v>
+        <v>0.16235249885171</v>
       </c>
       <c r="C72">
-        <v>-2112.357590344232</v>
+        <v>-2184.571100806187</v>
       </c>
       <c r="D72">
-        <v>1116.306330639751</v>
+        <v>1101.460876191854</v>
       </c>
       <c r="E72">
-        <v>2896.058319578294</v>
+        <v>2953.42637559235</v>
       </c>
       <c r="F72">
-        <v>4015.763920983984</v>
+        <v>4073.131976998041</v>
       </c>
       <c r="G72">
         <v>787.1</v>
@@ -7191,37 +7191,37 @@
         <v>428.91</v>
       </c>
       <c r="M72">
-        <v>806.365395333584</v>
+        <v>817.8849009812067</v>
       </c>
       <c r="N72">
-        <v>-377.455395333584</v>
+        <v>-388.9749009812066</v>
       </c>
       <c r="O72">
-        <v>-94.36384883339601</v>
+        <v>-97.24372524530166</v>
       </c>
       <c r="P72">
-        <v>-283.091546500188</v>
+        <v>-291.731175735905</v>
       </c>
       <c r="Q72">
-        <v>143.608453499812</v>
+        <v>134.968824264095</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1297788329822492</v>
+        <v>0.1326746548092233</v>
       </c>
       <c r="T72">
-        <v>1.636903764543667</v>
+        <v>1.693348721941725</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1329763164695842</v>
+        <v>0.1311034106038154</v>
       </c>
       <c r="W72">
-        <v>0.1740983556529075</v>
+        <v>0.1744744351507539</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5319052658783365</v>
+        <v>0.5244136424152614</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.16235249885171</v>
+        <v>0.16390249885171</v>
       </c>
       <c r="C73">
-        <v>-2184.571100806186</v>
+        <v>-2256.394942046608</v>
       </c>
       <c r="D73">
-        <v>1101.460876191855</v>
+        <v>1087.005090965489</v>
       </c>
       <c r="E73">
-        <v>2953.42637559235</v>
+        <v>3010.794431606407</v>
       </c>
       <c r="F73">
-        <v>4073.13197699804</v>
+        <v>4130.500033012097</v>
       </c>
       <c r="G73">
         <v>787.1</v>
@@ -7273,37 +7273,37 @@
         <v>428.91</v>
       </c>
       <c r="M73">
-        <v>817.8849009812066</v>
+        <v>829.4044066288292</v>
       </c>
       <c r="N73">
-        <v>-388.9749009812065</v>
+        <v>-400.4944066288292</v>
       </c>
       <c r="O73">
-        <v>-97.24372524530163</v>
+        <v>-100.1236016572073</v>
       </c>
       <c r="P73">
-        <v>-291.7311757359049</v>
+        <v>-300.3708049716219</v>
       </c>
       <c r="Q73">
-        <v>134.9688242640951</v>
+        <v>126.3291950283781</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1326746548092232</v>
+        <v>0.1357773210524098</v>
       </c>
       <c r="T73">
-        <v>1.693348721941724</v>
+        <v>1.753825462011072</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1311034106038154</v>
+        <v>0.1292825299009846</v>
       </c>
       <c r="W73">
-        <v>0.1744744351507539</v>
+        <v>0.1748400679958823</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5244136424152614</v>
+        <v>0.5171301196039384</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.16390249885171</v>
+        <v>0.16545249885171</v>
       </c>
       <c r="C74">
-        <v>-2256.394942046608</v>
+        <v>-2327.844257601133</v>
       </c>
       <c r="D74">
-        <v>1087.005090965489</v>
+        <v>1072.923831425021</v>
       </c>
       <c r="E74">
-        <v>3010.794431606407</v>
+        <v>3068.162487620463</v>
       </c>
       <c r="F74">
-        <v>4130.500033012097</v>
+        <v>4187.868089026154</v>
       </c>
       <c r="G74">
         <v>787.1</v>
@@ -7355,37 +7355,37 @@
         <v>428.91</v>
       </c>
       <c r="M74">
-        <v>829.4044066288292</v>
+        <v>840.9239122764517</v>
       </c>
       <c r="N74">
-        <v>-400.4944066288292</v>
+        <v>-412.0139122764517</v>
       </c>
       <c r="O74">
-        <v>-100.1236016572073</v>
+        <v>-103.0034780691129</v>
       </c>
       <c r="P74">
-        <v>-300.3708049716219</v>
+        <v>-309.0104342073387</v>
       </c>
       <c r="Q74">
-        <v>126.3291950283781</v>
+        <v>117.6895657926613</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1357773210524098</v>
+        <v>0.1391098144247213</v>
       </c>
       <c r="T74">
-        <v>1.753825462011072</v>
+        <v>1.818781960604074</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1292825299009846</v>
+        <v>0.1275115363406972</v>
       </c>
       <c r="W74">
-        <v>0.1748400679958823</v>
+        <v>0.175195683502788</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5171301196039384</v>
+        <v>0.5100461453627887</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.16545249885171</v>
+        <v>0.16700249885171</v>
       </c>
       <c r="C75">
-        <v>-2327.844257601133</v>
+        <v>-2398.933416352053</v>
       </c>
       <c r="D75">
-        <v>1072.923831425021</v>
+        <v>1059.202728688158</v>
       </c>
       <c r="E75">
-        <v>3068.162487620463</v>
+        <v>3125.530543634521</v>
       </c>
       <c r="F75">
-        <v>4187.868089026154</v>
+        <v>4245.236145040211</v>
       </c>
       <c r="G75">
         <v>787.1</v>
@@ -7437,37 +7437,37 @@
         <v>428.91</v>
       </c>
       <c r="M75">
-        <v>840.9239122764517</v>
+        <v>852.4434179240744</v>
       </c>
       <c r="N75">
-        <v>-412.0139122764517</v>
+        <v>-423.5334179240744</v>
       </c>
       <c r="O75">
-        <v>-103.0034780691129</v>
+        <v>-105.8833544810186</v>
       </c>
       <c r="P75">
-        <v>-309.0104342073387</v>
+        <v>-317.6500634430558</v>
       </c>
       <c r="Q75">
-        <v>117.6895657926613</v>
+        <v>109.0499365569442</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1391098144247213</v>
+        <v>0.1426986534410567</v>
       </c>
       <c r="T75">
-        <v>1.818781960604074</v>
+        <v>1.888735112935</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1275115363406972</v>
+        <v>0.1257884074712283</v>
       </c>
       <c r="W75">
-        <v>0.175195683502788</v>
+        <v>0.1755416877797774</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5100461453627887</v>
+        <v>0.5031536298849131</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.16700249885171</v>
+        <v>0.1951863124267103</v>
       </c>
       <c r="C76">
-        <v>-2398.933416352053</v>
+        <v>-2656.134855750042</v>
       </c>
       <c r="D76">
-        <v>1059.202728688158</v>
+        <v>859.3693453042257</v>
       </c>
       <c r="E76">
-        <v>3125.530543634521</v>
+        <v>3182.898599648577</v>
       </c>
       <c r="F76">
-        <v>4245.236145040211</v>
+        <v>4302.604201054268</v>
       </c>
       <c r="G76">
         <v>787.1</v>
@@ -7519,45 +7519,45 @@
         <v>428.91</v>
       </c>
       <c r="M76">
-        <v>852.4434179240744</v>
+        <v>1014.554070608596</v>
       </c>
       <c r="N76">
-        <v>-423.5334179240744</v>
+        <v>-585.6440706085964</v>
       </c>
       <c r="O76">
-        <v>-105.8833544810186</v>
+        <v>-146.4110176521491</v>
       </c>
       <c r="P76">
-        <v>-317.6500634430558</v>
+        <v>-439.2330529564473</v>
       </c>
       <c r="Q76">
-        <v>109.0499365569442</v>
+        <v>-12.53305295644731</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1426986534410567</v>
+        <v>0.1481098538787002</v>
       </c>
       <c r="T76">
-        <v>1.888735112935</v>
+        <v>1.994209481326751</v>
       </c>
       <c r="U76">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1257884074712283</v>
+        <v>0.105689290602006</v>
       </c>
       <c r="W76">
-        <v>0.1755416877797774</v>
+        <v>0.210878465276047</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.5031536298849131</v>
+        <v>0.4227571624080237</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1951863124267103</v>
+        <v>0.1970863124267103</v>
       </c>
       <c r="C77">
-        <v>-2656.134855750042</v>
+        <v>-2724.295704118458</v>
       </c>
       <c r="D77">
-        <v>859.3693453042257</v>
+        <v>848.5765529498674</v>
       </c>
       <c r="E77">
-        <v>3182.898599648577</v>
+        <v>3240.266655662635</v>
       </c>
       <c r="F77">
-        <v>4302.604201054268</v>
+        <v>4359.972257068325</v>
       </c>
       <c r="G77">
         <v>787.1</v>
@@ -7601,37 +7601,37 @@
         <v>428.91</v>
       </c>
       <c r="M77">
-        <v>1014.554070608596</v>
+        <v>1028.081458216711</v>
       </c>
       <c r="N77">
-        <v>-585.6440706085964</v>
+        <v>-599.171458216711</v>
       </c>
       <c r="O77">
-        <v>-146.4110176521491</v>
+        <v>-149.7928645541778</v>
       </c>
       <c r="P77">
-        <v>-439.2330529564473</v>
+        <v>-449.3785936625333</v>
       </c>
       <c r="Q77">
-        <v>-12.53305295644731</v>
+        <v>-22.67859366253327</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1481098538787002</v>
+        <v>0.1523727644569794</v>
       </c>
       <c r="T77">
-        <v>1.994209481326751</v>
+        <v>2.077301543048699</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.105689290602006</v>
+        <v>0.1042986420414532</v>
       </c>
       <c r="W77">
-        <v>0.210878465276047</v>
+        <v>0.2112063802066253</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4227571624080237</v>
+        <v>0.417194568165813</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1970863124267103</v>
+        <v>0.1989863124267103</v>
       </c>
       <c r="C78">
-        <v>-2724.295704118458</v>
+        <v>-2792.188822228882</v>
       </c>
       <c r="D78">
-        <v>848.5765529498674</v>
+        <v>838.0514908535004</v>
       </c>
       <c r="E78">
-        <v>3240.266655662635</v>
+        <v>3297.634711676692</v>
       </c>
       <c r="F78">
-        <v>4359.972257068325</v>
+        <v>4417.340313082383</v>
       </c>
       <c r="G78">
         <v>787.1</v>
@@ -7683,37 +7683,37 @@
         <v>428.91</v>
       </c>
       <c r="M78">
-        <v>1028.081458216711</v>
+        <v>1041.608845824826</v>
       </c>
       <c r="N78">
-        <v>-599.171458216711</v>
+        <v>-612.6988458248259</v>
       </c>
       <c r="O78">
-        <v>-149.7928645541778</v>
+        <v>-153.1747114562065</v>
       </c>
       <c r="P78">
-        <v>-449.3785936625333</v>
+        <v>-459.5241343686194</v>
       </c>
       <c r="Q78">
-        <v>-22.67859366253327</v>
+        <v>-32.82413436861941</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1523727644569794</v>
+        <v>0.1570063629116307</v>
       </c>
       <c r="T78">
-        <v>2.077301543048699</v>
+        <v>2.16761900144212</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1042986420414532</v>
+        <v>0.102944114222733</v>
       </c>
       <c r="W78">
-        <v>0.2112063802066253</v>
+        <v>0.2115257778662796</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.417194568165813</v>
+        <v>0.4117764568909322</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1989863124267103</v>
+        <v>0.2008863124267103</v>
       </c>
       <c r="C79">
-        <v>-2792.188822228882</v>
+        <v>-2859.824050166149</v>
       </c>
       <c r="D79">
-        <v>838.0514908535004</v>
+        <v>827.7843189302897</v>
       </c>
       <c r="E79">
-        <v>3297.634711676692</v>
+        <v>3355.002767690748</v>
       </c>
       <c r="F79">
-        <v>4417.340313082383</v>
+        <v>4474.708369096439</v>
       </c>
       <c r="G79">
         <v>787.1</v>
@@ -7765,37 +7765,37 @@
         <v>428.91</v>
       </c>
       <c r="M79">
-        <v>1041.608845824826</v>
+        <v>1055.13623343294</v>
       </c>
       <c r="N79">
-        <v>-612.6988458248259</v>
+        <v>-626.2262334329403</v>
       </c>
       <c r="O79">
-        <v>-153.1747114562065</v>
+        <v>-156.5565583582351</v>
       </c>
       <c r="P79">
-        <v>-459.5241343686194</v>
+        <v>-469.6696750747052</v>
       </c>
       <c r="Q79">
-        <v>-32.82413436861941</v>
+        <v>-42.96967507470521</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1570063629116307</v>
+        <v>0.162061197589432</v>
       </c>
       <c r="T79">
-        <v>2.16761900144212</v>
+        <v>2.266147137871307</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.102944114222733</v>
+        <v>0.1016243178865442</v>
       </c>
       <c r="W79">
-        <v>0.2115257778662796</v>
+        <v>0.2118369858423529</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4117764568909322</v>
+        <v>0.4064972715461768</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2008863124267103</v>
+        <v>0.2027863124267103</v>
       </c>
       <c r="C80">
-        <v>-2859.824050166149</v>
+        <v>-2927.210751638242</v>
       </c>
       <c r="D80">
-        <v>827.7843189302897</v>
+        <v>817.7656734722542</v>
       </c>
       <c r="E80">
-        <v>3355.002767690748</v>
+        <v>3412.370823704806</v>
       </c>
       <c r="F80">
-        <v>4474.708369096439</v>
+        <v>4532.076425110497</v>
       </c>
       <c r="G80">
         <v>787.1</v>
@@ -7847,37 +7847,37 @@
         <v>428.91</v>
       </c>
       <c r="M80">
-        <v>1055.13623343294</v>
+        <v>1068.663621041055</v>
       </c>
       <c r="N80">
-        <v>-626.2262334329403</v>
+        <v>-639.7536210410551</v>
       </c>
       <c r="O80">
-        <v>-156.5565583582351</v>
+        <v>-159.9384052602638</v>
       </c>
       <c r="P80">
-        <v>-469.6696750747052</v>
+        <v>-479.8152157807913</v>
       </c>
       <c r="Q80">
-        <v>-42.96967507470521</v>
+        <v>-53.11521578079135</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.162061197589432</v>
+        <v>0.1675974450936908</v>
       </c>
       <c r="T80">
-        <v>2.266147137871307</v>
+        <v>2.374058906341371</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1016243178865442</v>
+        <v>0.1003379341158284</v>
       </c>
       <c r="W80">
-        <v>0.2118369858423529</v>
+        <v>0.2121403151354877</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4064972715461768</v>
+        <v>0.4013517364633137</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2027863124267103</v>
+        <v>0.2046863124267103</v>
       </c>
       <c r="C81">
-        <v>-2927.210751638242</v>
+        <v>-2994.357842459428</v>
       </c>
       <c r="D81">
-        <v>817.7656734722542</v>
+        <v>807.9866386651256</v>
       </c>
       <c r="E81">
-        <v>3412.370823704806</v>
+        <v>3469.738879718862</v>
       </c>
       <c r="F81">
-        <v>4532.076425110497</v>
+        <v>4589.444481124553</v>
       </c>
       <c r="G81">
         <v>787.1</v>
@@ -7929,37 +7929,37 @@
         <v>428.91</v>
       </c>
       <c r="M81">
-        <v>1068.663621041055</v>
+        <v>1082.19100864917</v>
       </c>
       <c r="N81">
-        <v>-639.7536210410551</v>
+        <v>-653.2810086491695</v>
       </c>
       <c r="O81">
-        <v>-159.9384052602638</v>
+        <v>-163.3202521622924</v>
       </c>
       <c r="P81">
-        <v>-479.8152157807913</v>
+        <v>-489.9607564868771</v>
       </c>
       <c r="Q81">
-        <v>-53.11521578079135</v>
+        <v>-63.26075648687714</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1675974450936908</v>
+        <v>0.1736873173483753</v>
       </c>
       <c r="T81">
-        <v>2.374058906341371</v>
+        <v>2.492761851658439</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1003379341158284</v>
+        <v>0.09908370993938057</v>
       </c>
       <c r="W81">
-        <v>0.2121403151354877</v>
+        <v>0.2124360611962941</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4013517364633137</v>
+        <v>0.3963348397575224</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2046863124267103</v>
+        <v>0.2065863124267104</v>
       </c>
       <c r="C82">
-        <v>-2994.357842459428</v>
+        <v>-3061.2738170139</v>
       </c>
       <c r="D82">
-        <v>807.9866386651256</v>
+        <v>798.4387201247107</v>
       </c>
       <c r="E82">
-        <v>3469.738879718862</v>
+        <v>3527.10693573292</v>
       </c>
       <c r="F82">
-        <v>4589.444481124553</v>
+        <v>4646.81253713861</v>
       </c>
       <c r="G82">
         <v>787.1</v>
@@ -8011,37 +8011,37 @@
         <v>428.91</v>
       </c>
       <c r="M82">
-        <v>1082.19100864917</v>
+        <v>1095.718396257284</v>
       </c>
       <c r="N82">
-        <v>-653.2810086491695</v>
+        <v>-666.8083962572844</v>
       </c>
       <c r="O82">
-        <v>-163.3202521622924</v>
+        <v>-166.7020990643211</v>
       </c>
       <c r="P82">
-        <v>-489.9607564868771</v>
+        <v>-500.1062971929633</v>
       </c>
       <c r="Q82">
-        <v>-63.26075648687714</v>
+        <v>-73.40629719296328</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1736873173483753</v>
+        <v>0.1804182287877635</v>
       </c>
       <c r="T82">
-        <v>2.492761851658439</v>
+        <v>2.623959843850989</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09908370993938057</v>
+        <v>0.09786045426111659</v>
       </c>
       <c r="W82">
-        <v>0.2124360611962941</v>
+        <v>0.2127245048852287</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3963348397575224</v>
+        <v>0.3914418170444665</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2065863124267104</v>
+        <v>0.2084863124267103</v>
       </c>
       <c r="C83">
-        <v>-3061.2738170139</v>
+        <v>-3127.966772864999</v>
       </c>
       <c r="D83">
-        <v>798.4387201247107</v>
+        <v>789.1138202876682</v>
       </c>
       <c r="E83">
-        <v>3527.10693573292</v>
+        <v>3584.474991746976</v>
       </c>
       <c r="F83">
-        <v>4646.81253713861</v>
+        <v>4704.180593152667</v>
       </c>
       <c r="G83">
         <v>787.1</v>
@@ -8093,37 +8093,37 @@
         <v>428.91</v>
       </c>
       <c r="M83">
-        <v>1095.718396257284</v>
+        <v>1109.245783865399</v>
       </c>
       <c r="N83">
-        <v>-666.8083962572844</v>
+        <v>-680.3357838653988</v>
       </c>
       <c r="O83">
-        <v>-166.7020990643211</v>
+        <v>-170.0839459663497</v>
       </c>
       <c r="P83">
-        <v>-500.1062971929633</v>
+        <v>-510.2518378990491</v>
       </c>
       <c r="Q83">
-        <v>-73.40629719296328</v>
+        <v>-83.55183789904908</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1804182287877635</v>
+        <v>0.1878970192759726</v>
       </c>
       <c r="T83">
-        <v>2.623959843850989</v>
+        <v>2.769735390731599</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09786045426111659</v>
+        <v>0.09666703408720055</v>
       </c>
       <c r="W83">
-        <v>0.2127245048852287</v>
+        <v>0.2130059133622381</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3914418170444665</v>
+        <v>0.3866681363488023</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2084863124267103</v>
+        <v>0.2103863124267103</v>
       </c>
       <c r="C84">
-        <v>-3127.966772864999</v>
+        <v>-3194.444433659916</v>
       </c>
       <c r="D84">
-        <v>789.1138202876682</v>
+        <v>780.0042155068078</v>
       </c>
       <c r="E84">
-        <v>3584.474991746976</v>
+        <v>3641.843047761034</v>
       </c>
       <c r="F84">
-        <v>4704.180593152667</v>
+        <v>4761.548649166724</v>
       </c>
       <c r="G84">
         <v>787.1</v>
@@ -8175,37 +8175,37 @@
         <v>428.91</v>
       </c>
       <c r="M84">
-        <v>1109.245783865399</v>
+        <v>1122.773171473514</v>
       </c>
       <c r="N84">
-        <v>-680.3357838653988</v>
+        <v>-693.8631714735136</v>
       </c>
       <c r="O84">
-        <v>-170.0839459663497</v>
+        <v>-173.4657928683784</v>
       </c>
       <c r="P84">
-        <v>-510.2518378990491</v>
+        <v>-520.3973786051351</v>
       </c>
       <c r="Q84">
-        <v>-83.55183789904908</v>
+        <v>-93.69737860513516</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1878970192759726</v>
+        <v>0.1962556674686769</v>
       </c>
       <c r="T84">
-        <v>2.769735390731599</v>
+        <v>2.932661001951105</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09666703408720055</v>
+        <v>0.09550237102590896</v>
       </c>
       <c r="W84">
-        <v>0.2130059133622381</v>
+        <v>0.2132805409120907</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3866681363488023</v>
+        <v>0.3820094841036359</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2103863124267103</v>
+        <v>0.2122863124267103</v>
       </c>
       <c r="C85">
-        <v>-3194.444433659916</v>
+        <v>-3260.714170465991</v>
       </c>
       <c r="D85">
-        <v>780.0042155068078</v>
+        <v>771.1025347147896</v>
       </c>
       <c r="E85">
-        <v>3641.843047761034</v>
+        <v>3699.21110377509</v>
       </c>
       <c r="F85">
-        <v>4761.548649166724</v>
+        <v>4818.916705180781</v>
       </c>
       <c r="G85">
         <v>787.1</v>
@@ -8257,37 +8257,37 @@
         <v>428.91</v>
       </c>
       <c r="M85">
-        <v>1122.773171473514</v>
+        <v>1136.300559081628</v>
       </c>
       <c r="N85">
-        <v>-693.8631714735136</v>
+        <v>-707.390559081628</v>
       </c>
       <c r="O85">
-        <v>-173.4657928683784</v>
+        <v>-176.847639770407</v>
       </c>
       <c r="P85">
-        <v>-520.3973786051351</v>
+        <v>-530.542919311221</v>
       </c>
       <c r="Q85">
-        <v>-93.69737860513516</v>
+        <v>-103.842919311221</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1962556674686769</v>
+        <v>0.2056591466854692</v>
       </c>
       <c r="T85">
-        <v>2.932661001951105</v>
+        <v>3.11595231457305</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09550237102590896</v>
+        <v>0.0943654380375053</v>
       </c>
       <c r="W85">
-        <v>0.2132805409120907</v>
+        <v>0.2135486297107562</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3820094841036359</v>
+        <v>0.3774617521500212</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2122863124267103</v>
+        <v>0.2141863124267103</v>
       </c>
       <c r="C86">
-        <v>-3260.71417046599</v>
+        <v>-3326.783021662529</v>
       </c>
       <c r="D86">
-        <v>771.1025347147896</v>
+        <v>762.4017395323079</v>
       </c>
       <c r="E86">
-        <v>3699.211103775089</v>
+        <v>3756.579159789147</v>
       </c>
       <c r="F86">
-        <v>4818.91670518078</v>
+        <v>4876.284761194837</v>
       </c>
       <c r="G86">
         <v>787.1</v>
@@ -8339,37 +8339,37 @@
         <v>428.91</v>
       </c>
       <c r="M86">
-        <v>1136.300559081628</v>
+        <v>1149.827946689743</v>
       </c>
       <c r="N86">
-        <v>-707.3905590816278</v>
+        <v>-720.9179466897426</v>
       </c>
       <c r="O86">
-        <v>-176.8476397704069</v>
+        <v>-180.2294866724357</v>
       </c>
       <c r="P86">
-        <v>-530.5429193112209</v>
+        <v>-540.688460017307</v>
       </c>
       <c r="Q86">
-        <v>-103.8429193112209</v>
+        <v>-113.988460017307</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2056591466854691</v>
+        <v>0.216316423131167</v>
       </c>
       <c r="T86">
-        <v>3.115952314573047</v>
+        <v>3.323682468877918</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09436543803750531</v>
+        <v>0.09325525641353465</v>
       </c>
       <c r="W86">
-        <v>0.2135486297107562</v>
+        <v>0.2138104105376885</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3774617521500213</v>
+        <v>0.3730210256541386</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2141863124267103</v>
+        <v>0.2160863124267103</v>
       </c>
       <c r="C87">
-        <v>-3326.783021662529</v>
+        <v>-3392.657711500927</v>
       </c>
       <c r="D87">
-        <v>762.4017395323079</v>
+        <v>753.895105707967</v>
       </c>
       <c r="E87">
-        <v>3756.579159789147</v>
+        <v>3813.947215803203</v>
       </c>
       <c r="F87">
-        <v>4876.284761194837</v>
+        <v>4933.652817208894</v>
       </c>
       <c r="G87">
         <v>787.1</v>
@@ -8421,37 +8421,37 @@
         <v>428.91</v>
       </c>
       <c r="M87">
-        <v>1149.827946689743</v>
+        <v>1163.355334297857</v>
       </c>
       <c r="N87">
-        <v>-720.9179466897426</v>
+        <v>-734.445334297857</v>
       </c>
       <c r="O87">
-        <v>-180.2294866724357</v>
+        <v>-183.6113335744643</v>
       </c>
       <c r="P87">
-        <v>-540.688460017307</v>
+        <v>-550.8340007233928</v>
       </c>
       <c r="Q87">
-        <v>-113.988460017307</v>
+        <v>-124.1340007233928</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.216316423131167</v>
+        <v>0.2284961676405361</v>
       </c>
       <c r="T87">
-        <v>3.323682468877918</v>
+        <v>3.561088359512054</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09325525641353465</v>
+        <v>0.09217089296686566</v>
       </c>
       <c r="W87">
-        <v>0.2138104105376885</v>
+        <v>0.2140661034384131</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3730210256541386</v>
+        <v>0.3686835718674627</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2160863124267103</v>
+        <v>0.2179863124267103</v>
       </c>
       <c r="C88">
-        <v>-3392.657711500927</v>
+        <v>-3458.344667435993</v>
       </c>
       <c r="D88">
-        <v>753.895105707967</v>
+        <v>745.5762057869584</v>
       </c>
       <c r="E88">
-        <v>3813.947215803203</v>
+        <v>3871.315271817261</v>
       </c>
       <c r="F88">
-        <v>4933.652817208894</v>
+        <v>4991.020873222951</v>
       </c>
       <c r="G88">
         <v>787.1</v>
@@ -8503,37 +8503,37 @@
         <v>428.91</v>
       </c>
       <c r="M88">
-        <v>1163.355334297857</v>
+        <v>1176.882721905972</v>
       </c>
       <c r="N88">
-        <v>-734.445334297857</v>
+        <v>-747.9727219059719</v>
       </c>
       <c r="O88">
-        <v>-183.6113335744643</v>
+        <v>-186.993180476493</v>
       </c>
       <c r="P88">
-        <v>-550.8340007233928</v>
+        <v>-560.9795414294789</v>
       </c>
       <c r="Q88">
-        <v>-124.1340007233928</v>
+        <v>-134.2795414294789</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2284961676405361</v>
+        <v>0.2425497189975004</v>
       </c>
       <c r="T88">
-        <v>3.561088359512054</v>
+        <v>3.835018233320674</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09217089296686566</v>
+        <v>0.09111145741552236</v>
       </c>
       <c r="W88">
-        <v>0.2140661034384131</v>
+        <v>0.2143159183414198</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3686835718674627</v>
+        <v>0.3644458296620895</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2179863124267103</v>
+        <v>0.2198863124267103</v>
       </c>
       <c r="C89">
-        <v>-3458.344667435993</v>
+        <v>-3523.850036322316</v>
       </c>
       <c r="D89">
-        <v>745.5762057869584</v>
+        <v>737.438892914693</v>
       </c>
       <c r="E89">
-        <v>3871.315271817261</v>
+        <v>3928.683327831318</v>
       </c>
       <c r="F89">
-        <v>4991.020873222951</v>
+        <v>5048.388929237009</v>
       </c>
       <c r="G89">
         <v>787.1</v>
@@ -8585,37 +8585,37 @@
         <v>428.91</v>
       </c>
       <c r="M89">
-        <v>1176.882721905972</v>
+        <v>1190.410109514087</v>
       </c>
       <c r="N89">
-        <v>-747.9727219059719</v>
+        <v>-761.5001095140865</v>
       </c>
       <c r="O89">
-        <v>-186.993180476493</v>
+        <v>-190.3750273785216</v>
       </c>
       <c r="P89">
-        <v>-560.9795414294789</v>
+        <v>-571.1250821355649</v>
       </c>
       <c r="Q89">
-        <v>-134.2795414294789</v>
+        <v>-144.4250821355649</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2425497189975004</v>
+        <v>0.2589455289139588</v>
       </c>
       <c r="T89">
-        <v>3.835018233320674</v>
+        <v>4.154603086097397</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09111145741552236</v>
+        <v>0.09007609994489142</v>
       </c>
       <c r="W89">
-        <v>0.2143159183414198</v>
+        <v>0.2145600556329946</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3644458296620895</v>
+        <v>0.3603043997795657</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2198863124267103</v>
+        <v>0.2217863124267103</v>
       </c>
       <c r="C90">
-        <v>-3523.850036322316</v>
+        <v>-3589.179699561487</v>
       </c>
       <c r="D90">
-        <v>737.438892914693</v>
+        <v>729.4772856895778</v>
       </c>
       <c r="E90">
-        <v>3928.683327831318</v>
+        <v>3986.051383845374</v>
       </c>
       <c r="F90">
-        <v>5048.388929237009</v>
+        <v>5105.756985251065</v>
       </c>
       <c r="G90">
         <v>787.1</v>
@@ -8667,37 +8667,37 @@
         <v>428.91</v>
       </c>
       <c r="M90">
-        <v>1190.410109514087</v>
+        <v>1203.937497122201</v>
       </c>
       <c r="N90">
-        <v>-761.5001095140865</v>
+        <v>-775.0274971222011</v>
       </c>
       <c r="O90">
-        <v>-190.3750273785216</v>
+        <v>-193.7568742805503</v>
       </c>
       <c r="P90">
-        <v>-571.1250821355649</v>
+        <v>-581.2706228416508</v>
       </c>
       <c r="Q90">
-        <v>-144.4250821355649</v>
+        <v>-154.5706228416508</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2589455289139588</v>
+        <v>0.2783223951788641</v>
       </c>
       <c r="T90">
-        <v>4.154603086097397</v>
+        <v>4.532294275742615</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09007609994489142</v>
+        <v>0.08906400893427467</v>
       </c>
       <c r="W90">
-        <v>0.2145600556329946</v>
+        <v>0.214798706693298</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3603043997795657</v>
+        <v>0.3562560357370987</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2217863124267103</v>
+        <v>0.2236863124267103</v>
       </c>
       <c r="C91">
-        <v>-3589.179699561487</v>
+        <v>-3654.339287278589</v>
       </c>
       <c r="D91">
-        <v>729.4772856895778</v>
+        <v>721.6857539865334</v>
       </c>
       <c r="E91">
-        <v>3986.051383845374</v>
+        <v>4043.419439859432</v>
       </c>
       <c r="F91">
-        <v>5105.756985251065</v>
+        <v>5163.125041265122</v>
       </c>
       <c r="G91">
         <v>787.1</v>
@@ -8749,37 +8749,37 @@
         <v>428.91</v>
       </c>
       <c r="M91">
-        <v>1203.937497122201</v>
+        <v>1217.464884730316</v>
       </c>
       <c r="N91">
-        <v>-775.0274971222011</v>
+        <v>-788.554884730316</v>
       </c>
       <c r="O91">
-        <v>-193.7568742805503</v>
+        <v>-197.138721182579</v>
       </c>
       <c r="P91">
-        <v>-581.2706228416508</v>
+        <v>-591.4161635477369</v>
       </c>
       <c r="Q91">
-        <v>-154.5706228416508</v>
+        <v>-164.7161635477369</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2783223951788641</v>
+        <v>0.3015746346967506</v>
       </c>
       <c r="T91">
-        <v>4.532294275742615</v>
+        <v>4.985523703316877</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08906400893427467</v>
+        <v>0.08807440883500493</v>
       </c>
       <c r="W91">
-        <v>0.214798706693298</v>
+        <v>0.2150320543967058</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3562560357370987</v>
+        <v>0.3522976353400198</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2236863124267103</v>
+        <v>0.2255863124267103</v>
       </c>
       <c r="C92">
-        <v>-3654.339287278589</v>
+        <v>-3719.334191599762</v>
       </c>
       <c r="D92">
-        <v>721.6857539865334</v>
+        <v>714.0589056794167</v>
       </c>
       <c r="E92">
-        <v>4043.419439859432</v>
+        <v>4100.787495873488</v>
       </c>
       <c r="F92">
-        <v>5163.125041265122</v>
+        <v>5220.493097279179</v>
       </c>
       <c r="G92">
         <v>787.1</v>
@@ -8831,37 +8831,37 @@
         <v>428.91</v>
       </c>
       <c r="M92">
-        <v>1217.464884730316</v>
+        <v>1230.99227233843</v>
       </c>
       <c r="N92">
-        <v>-788.554884730316</v>
+        <v>-802.0822723384304</v>
       </c>
       <c r="O92">
-        <v>-197.138721182579</v>
+        <v>-200.5205680846076</v>
       </c>
       <c r="P92">
-        <v>-591.4161635477369</v>
+        <v>-601.5617042538228</v>
       </c>
       <c r="Q92">
-        <v>-164.7161635477369</v>
+        <v>-174.8617042538228</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3015746346967506</v>
+        <v>0.3299940385519451</v>
       </c>
       <c r="T92">
-        <v>4.985523703316877</v>
+        <v>5.539470781463197</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08807440883500493</v>
+        <v>0.08710655818846642</v>
       </c>
       <c r="W92">
-        <v>0.2150320543967058</v>
+        <v>0.2152602735791596</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3522976353400198</v>
+        <v>0.3484262327538657</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2255863124267103</v>
+        <v>0.2274863124267103</v>
       </c>
       <c r="C93">
-        <v>-3719.334191599762</v>
+        <v>-3784.169579096691</v>
       </c>
       <c r="D93">
-        <v>714.0589056794167</v>
+        <v>706.5915741965456</v>
       </c>
       <c r="E93">
-        <v>4100.787495873488</v>
+        <v>4158.155551887546</v>
       </c>
       <c r="F93">
-        <v>5220.493097279179</v>
+        <v>5277.861153293236</v>
       </c>
       <c r="G93">
         <v>787.1</v>
@@ -8913,37 +8913,37 @@
         <v>428.91</v>
       </c>
       <c r="M93">
-        <v>1230.99227233843</v>
+        <v>1244.519659946545</v>
       </c>
       <c r="N93">
-        <v>-802.0822723384304</v>
+        <v>-815.6096599465452</v>
       </c>
       <c r="O93">
-        <v>-200.5205680846076</v>
+        <v>-203.9024149866363</v>
       </c>
       <c r="P93">
-        <v>-601.5617042538228</v>
+        <v>-611.7072449599088</v>
       </c>
       <c r="Q93">
-        <v>-174.8617042538228</v>
+        <v>-185.0072449599089</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3299940385519451</v>
+        <v>0.3655182933709384</v>
       </c>
       <c r="T93">
-        <v>5.539470781463197</v>
+        <v>6.2319046291461</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08710655818846642</v>
+        <v>0.08615974777337439</v>
       </c>
       <c r="W93">
-        <v>0.2152602735791596</v>
+        <v>0.2154835314750383</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3484262327538657</v>
+        <v>0.3446389910934976</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2274863124267103</v>
+        <v>0.2293863124267103</v>
       </c>
       <c r="C94">
-        <v>-3784.169579096691</v>
+        <v>-3848.850402458309</v>
       </c>
       <c r="D94">
-        <v>706.5915741965456</v>
+        <v>699.2788068489834</v>
       </c>
       <c r="E94">
-        <v>4158.155551887546</v>
+        <v>4215.523607901602</v>
       </c>
       <c r="F94">
-        <v>5277.861153293236</v>
+        <v>5335.229209307293</v>
       </c>
       <c r="G94">
         <v>787.1</v>
@@ -8995,37 +8995,37 @@
         <v>428.91</v>
       </c>
       <c r="M94">
-        <v>1244.519659946545</v>
+        <v>1258.04704755466</v>
       </c>
       <c r="N94">
-        <v>-815.6096599465452</v>
+        <v>-829.1370475546596</v>
       </c>
       <c r="O94">
-        <v>-203.9024149866363</v>
+        <v>-207.2842618886649</v>
       </c>
       <c r="P94">
-        <v>-611.7072449599088</v>
+        <v>-621.8527856659947</v>
       </c>
       <c r="Q94">
-        <v>-185.0072449599089</v>
+        <v>-195.1527856659947</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3655182933709384</v>
+        <v>0.4111923352810725</v>
       </c>
       <c r="T94">
-        <v>6.2319046291461</v>
+        <v>7.122176719024115</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08615974777337439</v>
+        <v>0.08523329887258543</v>
       </c>
       <c r="W94">
-        <v>0.2154835314750383</v>
+        <v>0.2157019881258443</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3446389910934976</v>
+        <v>0.3409331954903417</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2293863124267103</v>
+        <v>0.2312863124267103</v>
       </c>
       <c r="C95">
-        <v>-3848.850402458309</v>
+        <v>-3913.38141144518</v>
       </c>
       <c r="D95">
-        <v>699.2788068489834</v>
+        <v>692.1158538761699</v>
       </c>
       <c r="E95">
-        <v>4215.523607901602</v>
+        <v>4272.89166391566</v>
       </c>
       <c r="F95">
-        <v>5335.229209307293</v>
+        <v>5392.59726532135</v>
       </c>
       <c r="G95">
         <v>787.1</v>
@@ -9077,37 +9077,37 @@
         <v>428.91</v>
       </c>
       <c r="M95">
-        <v>1258.04704755466</v>
+        <v>1271.574435162775</v>
       </c>
       <c r="N95">
-        <v>-829.1370475546596</v>
+        <v>-842.6644351627745</v>
       </c>
       <c r="O95">
-        <v>-207.2842618886649</v>
+        <v>-210.6661087906936</v>
       </c>
       <c r="P95">
-        <v>-621.8527856659947</v>
+        <v>-631.9983263720808</v>
       </c>
       <c r="Q95">
-        <v>-195.1527856659947</v>
+        <v>-205.2983263720808</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4111923352810725</v>
+        <v>0.472091057827918</v>
       </c>
       <c r="T95">
-        <v>7.122176719024115</v>
+        <v>8.309206172194802</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08523329887258543</v>
+        <v>0.08432656165053663</v>
       </c>
       <c r="W95">
-        <v>0.2157019881258443</v>
+        <v>0.2159157967628035</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3409331954903417</v>
+        <v>0.3373062466021466</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2312863124267103</v>
+        <v>0.2331863124267103</v>
       </c>
       <c r="C96">
-        <v>-3913.38141144518</v>
+        <v>-3977.767163177429</v>
       </c>
       <c r="D96">
-        <v>692.1158538761699</v>
+        <v>685.0981581579779</v>
       </c>
       <c r="E96">
-        <v>4272.89166391566</v>
+        <v>4330.259719929716</v>
       </c>
       <c r="F96">
-        <v>5392.59726532135</v>
+        <v>5449.965321335407</v>
       </c>
       <c r="G96">
         <v>787.1</v>
@@ -9159,37 +9159,37 @@
         <v>428.91</v>
       </c>
       <c r="M96">
-        <v>1271.574435162775</v>
+        <v>1285.101822770889</v>
       </c>
       <c r="N96">
-        <v>-842.6644351627745</v>
+        <v>-856.1918227708888</v>
       </c>
       <c r="O96">
-        <v>-210.6661087906936</v>
+        <v>-214.0479556927222</v>
       </c>
       <c r="P96">
-        <v>-631.9983263720808</v>
+        <v>-642.1438670781666</v>
       </c>
       <c r="Q96">
-        <v>-205.2983263720808</v>
+        <v>-215.4438670781666</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.472091057827918</v>
+        <v>0.5573492693935017</v>
       </c>
       <c r="T96">
-        <v>8.309206172194802</v>
+        <v>9.971047406633767</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08432656165053663</v>
+        <v>0.08343891363316258</v>
       </c>
       <c r="W96">
-        <v>0.2159157967628035</v>
+        <v>0.2161251041653003</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3373062466021466</v>
+        <v>0.3337556545326503</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2331863124267103</v>
+        <v>0.2350863124267103</v>
       </c>
       <c r="C97">
-        <v>-3977.767163177429</v>
+        <v>-4042.012031803091</v>
       </c>
       <c r="D97">
-        <v>685.0981581579779</v>
+        <v>678.2213455463727</v>
       </c>
       <c r="E97">
-        <v>4330.259719929716</v>
+        <v>4387.627775943773</v>
       </c>
       <c r="F97">
-        <v>5449.965321335407</v>
+        <v>5507.333377349464</v>
       </c>
       <c r="G97">
         <v>787.1</v>
@@ -9241,37 +9241,37 @@
         <v>428.91</v>
       </c>
       <c r="M97">
-        <v>1285.101822770889</v>
+        <v>1298.629210379004</v>
       </c>
       <c r="N97">
-        <v>-856.1918227708888</v>
+        <v>-869.7192103790037</v>
       </c>
       <c r="O97">
-        <v>-214.0479556927222</v>
+        <v>-217.4298025947509</v>
       </c>
       <c r="P97">
-        <v>-642.1438670781666</v>
+        <v>-652.2894077842527</v>
       </c>
       <c r="Q97">
-        <v>-215.4438670781666</v>
+        <v>-225.5894077842527</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5573492693935017</v>
+        <v>0.6852365867418775</v>
       </c>
       <c r="T97">
-        <v>9.971047406633767</v>
+        <v>12.46380925829221</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08343891363316258</v>
+        <v>0.08256975828281712</v>
       </c>
       <c r="W97">
-        <v>0.2161251041653003</v>
+        <v>0.2163300509969117</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3337556545326503</v>
+        <v>0.3302790331312685</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2350863124267103</v>
+        <v>0.2369863124267103</v>
       </c>
       <c r="C98">
-        <v>-4042.01203180309</v>
+        <v>-4106.120217589942</v>
       </c>
       <c r="D98">
-        <v>678.2213455463732</v>
+        <v>671.4812157735787</v>
       </c>
       <c r="E98">
-        <v>4387.627775943773</v>
+        <v>4444.995831957829</v>
       </c>
       <c r="F98">
-        <v>5507.333377349463</v>
+        <v>5564.70143336352</v>
       </c>
       <c r="G98">
         <v>787.1</v>
@@ -9323,37 +9323,37 @@
         <v>428.91</v>
       </c>
       <c r="M98">
-        <v>1298.629210379004</v>
+        <v>1312.156597987118</v>
       </c>
       <c r="N98">
-        <v>-869.7192103790035</v>
+        <v>-883.2465979871179</v>
       </c>
       <c r="O98">
-        <v>-217.4298025947509</v>
+        <v>-220.8116494967795</v>
       </c>
       <c r="P98">
-        <v>-652.2894077842526</v>
+        <v>-662.4349484903385</v>
       </c>
       <c r="Q98">
-        <v>-225.5894077842526</v>
+        <v>-235.7349484903385</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6852365867418758</v>
+        <v>0.8983821156558345</v>
       </c>
       <c r="T98">
-        <v>12.46380925829218</v>
+        <v>16.61841234438958</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08256975828281714</v>
+        <v>0.08171852366134481</v>
       </c>
       <c r="W98">
-        <v>0.2163300509969117</v>
+        <v>0.2165307721206549</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3302790331312686</v>
+        <v>0.3268740946453793</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2369863124267103</v>
+        <v>0.2388863124267104</v>
       </c>
       <c r="C99">
-        <v>-4106.120217589942</v>
+        <v>-4170.095755480552</v>
       </c>
       <c r="D99">
-        <v>671.4812157735787</v>
+        <v>664.8737338970255</v>
       </c>
       <c r="E99">
-        <v>4444.995831957829</v>
+        <v>4502.363887971886</v>
       </c>
       <c r="F99">
-        <v>5564.70143336352</v>
+        <v>5622.069489377577</v>
       </c>
       <c r="G99">
         <v>787.1</v>
@@ -9405,37 +9405,37 @@
         <v>428.91</v>
       </c>
       <c r="M99">
-        <v>1312.156597987118</v>
+        <v>1325.683985595233</v>
       </c>
       <c r="N99">
-        <v>-883.2465979871179</v>
+        <v>-896.7739855952327</v>
       </c>
       <c r="O99">
-        <v>-220.8116494967795</v>
+        <v>-224.1934963988082</v>
       </c>
       <c r="P99">
-        <v>-662.4349484903385</v>
+        <v>-672.5804891964245</v>
       </c>
       <c r="Q99">
-        <v>-235.7349484903385</v>
+        <v>-245.8804891964245</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8983821156558345</v>
+        <v>1.324673173483752</v>
       </c>
       <c r="T99">
-        <v>16.61841234438958</v>
+        <v>24.92761851658436</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08171852366134481</v>
+        <v>0.08088466117500454</v>
       </c>
       <c r="W99">
-        <v>0.2165307721206549</v>
+        <v>0.2167273968949339</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3268740946453793</v>
+        <v>0.3235386447000183</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2388863124267104</v>
+        <v>0.2407863124267103</v>
       </c>
       <c r="C100">
-        <v>-4170.095755480552</v>
+        <v>-4233.942523147145</v>
       </c>
       <c r="D100">
-        <v>664.8737338970255</v>
+        <v>658.3950222444881</v>
       </c>
       <c r="E100">
-        <v>4502.363887971886</v>
+        <v>4559.731943985943</v>
       </c>
       <c r="F100">
-        <v>5622.069489377577</v>
+        <v>5679.437545391634</v>
       </c>
       <c r="G100">
         <v>787.1</v>
@@ -9487,37 +9487,37 @@
         <v>428.91</v>
       </c>
       <c r="M100">
-        <v>1325.683985595233</v>
+        <v>1339.211373203347</v>
       </c>
       <c r="N100">
-        <v>-896.7739855952327</v>
+        <v>-910.3013732033471</v>
       </c>
       <c r="O100">
-        <v>-224.1934963988082</v>
+        <v>-227.5753433008368</v>
       </c>
       <c r="P100">
-        <v>-672.5804891964245</v>
+        <v>-682.7260299025104</v>
       </c>
       <c r="Q100">
-        <v>-245.8804891964245</v>
+        <v>-256.0260299025104</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.324673173483752</v>
+        <v>2.603546346967503</v>
       </c>
       <c r="T100">
-        <v>24.92761851658436</v>
+        <v>49.85523703316872</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08088466117500454</v>
+        <v>0.08006764439545905</v>
       </c>
       <c r="W100">
-        <v>0.2167273968949339</v>
+        <v>0.2169200494515507</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3235386447000183</v>
+        <v>0.3202705775818363</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2407863124267103</v>
-      </c>
-      <c r="C101">
-        <v>-4233.942523147145</v>
-      </c>
-      <c r="D101">
-        <v>658.3950222444881</v>
-      </c>
-      <c r="E101">
-        <v>4559.731943985943</v>
-      </c>
-      <c r="F101">
-        <v>5679.437545391634</v>
-      </c>
-      <c r="G101">
-        <v>787.1</v>
-      </c>
-      <c r="H101">
-        <v>4617.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>855.61</v>
-      </c>
-      <c r="K101">
-        <v>426.7</v>
-      </c>
-      <c r="L101">
-        <v>428.91</v>
-      </c>
-      <c r="M101">
-        <v>1339.211373203347</v>
-      </c>
-      <c r="N101">
-        <v>-910.3013732033471</v>
-      </c>
-      <c r="O101">
-        <v>-227.5753433008368</v>
-      </c>
-      <c r="P101">
-        <v>-682.7260299025104</v>
-      </c>
-      <c r="Q101">
-        <v>-256.0260299025104</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.603546346967503</v>
-      </c>
-      <c r="T101">
-        <v>49.85523703316872</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08006764439545905</v>
-      </c>
-      <c r="W101">
-        <v>0.2169200494515507</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3202705775818363</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
